--- a/docs/lab2/Lab02_BBT_TCs_Form (1).xlsx
+++ b/docs/lab2/Lab02_BBT_TCs_Form (1).xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40B5818-F9B5-4D75-A5AF-101ABC34D0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4788" yWindow="1056" windowWidth="17280" windowHeight="8880" tabRatio="522" activeTab="3"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="522" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -12,7 +13,7 @@
     <sheet name="F01.BVA" sheetId="3" r:id="rId3"/>
     <sheet name="BBT-TCs" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,12 +34,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="D16" authorId="0">
+    <comment ref="D16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -63,7 +64,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M17" authorId="0">
+    <comment ref="M17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -88,7 +89,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D22" authorId="0">
+    <comment ref="D22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -118,12 +119,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H18" authorId="0">
+    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -148,7 +149,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H26" authorId="0">
+    <comment ref="H26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -172,7 +173,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M26" authorId="0">
+    <comment ref="M26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -240,12 +241,6 @@
     <t>Informaţiile vor fi preluate din fişiere text.</t>
   </si>
   <si>
-    <t>1. Evidenţa filmelor din colecţia personală</t>
-  </si>
-  <si>
-    <t>Un cinefil doreşte să îşi dezvolte un program pentru gestionarea filmelor din colecţia personală. Programul va permite următoarele operaţii:</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -272,9 +267,6 @@
   </si>
   <si>
     <t xml:space="preserve">1. La proiectarea TCs se consideră o metodă care poate avea următoarea semnătură: </t>
-  </si>
-  <si>
-    <t>addMovie(String title, String director, int year, List&lt;String&gt; actors, String category, List&lt;String&gt; keywords): void</t>
   </si>
   <si>
     <t>2. Metoda este definită la nivelul repository, service sau ui.</t>
@@ -798,11 +790,20 @@
   <si>
     <t>Error message-? Invalid name</t>
   </si>
+  <si>
+    <t>addProduct ( id, nume, pret, categorie,tip): void;</t>
+  </si>
+  <si>
+    <t>1. Evidenţa bauturilor din magazin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gestiunea bauturilor </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="30">
     <font>
       <sz val="11"/>
@@ -1430,7 +1431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1534,36 +1535,169 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1591,9 +1725,6 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1603,37 +1734,40 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1648,145 +1782,6 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1805,9 +1800,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1845,7 +1840,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1917,7 +1912,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2090,7 +2085,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
@@ -2105,12 +2100,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10">
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="53"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="87"/>
       <c r="H1" s="38" t="s">
         <v>1</v>
       </c>
@@ -2118,11 +2113,11 @@
       <c r="J1" s="38"/>
     </row>
     <row r="2" spans="2:10">
-      <c r="H2" s="54" t="s">
+      <c r="H2" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
     </row>
     <row r="3" spans="2:10">
       <c r="H3" s="2"/>
@@ -2138,7 +2133,7 @@
         <v>5</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J4" s="2">
         <v>236</v>
@@ -2149,7 +2144,7 @@
         <v>6</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J5" s="2">
         <v>236</v>
@@ -2161,7 +2156,7 @@
         <v>7</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J6" s="2">
         <v>236</v>
@@ -2202,7 +2197,7 @@
     </row>
     <row r="14" spans="2:10">
       <c r="B14" t="s">
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -2210,7 +2205,7 @@
     </row>
     <row r="15" spans="2:10">
       <c r="B15" t="s">
-        <v>13</v>
+        <v>148</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -2218,7 +2213,7 @@
     </row>
     <row r="16" spans="2:10">
       <c r="B16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -2231,27 +2226,27 @@
     </row>
     <row r="18" spans="1:15">
       <c r="B18" s="36" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="B19" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="C20" s="34" t="s">
-        <v>17</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="B21" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="B22" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -2268,7 +2263,7 @@
     </row>
     <row r="23" spans="1:15">
       <c r="B23" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -2285,21 +2280,21 @@
     </row>
     <row r="24" spans="1:15" ht="14.4" customHeight="1">
       <c r="A24" s="35"/>
-      <c r="B24" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="50"/>
-      <c r="M24" s="50"/>
-      <c r="N24" s="50"/>
+      <c r="B24" s="93" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="93"/>
+      <c r="D24" s="93"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="93"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="93"/>
+      <c r="K24" s="93"/>
+      <c r="L24" s="93"/>
+      <c r="M24" s="93"/>
+      <c r="N24" s="93"/>
     </row>
     <row r="26" spans="1:15">
       <c r="C26" s="37"/>
@@ -2316,7 +2311,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
@@ -2341,185 +2336,185 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17">
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="53"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="87"/>
     </row>
     <row r="3" spans="2:17">
-      <c r="B3" s="59" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="61"/>
+      <c r="B3" s="104" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="106"/>
     </row>
     <row r="5" spans="2:17">
-      <c r="B5" s="62" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="G5" s="63" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="63"/>
-      <c r="N5" s="63"/>
-      <c r="O5" s="63"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
+      <c r="B5" s="107" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="G5" s="108" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="108"/>
+      <c r="M5" s="108"/>
+      <c r="N5" s="108"/>
+      <c r="O5" s="108"/>
+      <c r="P5" s="108"/>
+      <c r="Q5" s="108"/>
     </row>
     <row r="6" spans="2:17">
       <c r="B6" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="G6" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="H6" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="I6" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="77"/>
+      <c r="N6" s="77"/>
+      <c r="O6" s="78"/>
+      <c r="P6" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="72" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="75"/>
-      <c r="K6" s="75"/>
-      <c r="L6" s="75"/>
-      <c r="M6" s="75"/>
-      <c r="N6" s="75"/>
-      <c r="O6" s="71"/>
-      <c r="P6" s="74" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q6" s="74"/>
+      <c r="Q6" s="72"/>
     </row>
     <row r="7" spans="2:17">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="58" t="s">
-        <v>84</v>
+      <c r="C7" s="103" t="s">
+        <v>81</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="73"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="112"/>
       <c r="I7" s="18" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J7" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="K7" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="L7" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="N7" s="70"/>
-      <c r="O7" s="71"/>
-      <c r="P7" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q7" s="71"/>
+      <c r="N7" s="76"/>
+      <c r="O7" s="78"/>
+      <c r="P7" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q7" s="78"/>
     </row>
     <row r="8" spans="2:17">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="58"/>
+      <c r="C8" s="103"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G8" s="18">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I8" s="2">
         <v>123</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K8" s="2">
         <v>1</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="N8" s="68"/>
-      <c r="O8" s="69"/>
-      <c r="P8" s="68" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q8" s="69"/>
+        <v>93</v>
+      </c>
+      <c r="N8" s="95"/>
+      <c r="O8" s="96"/>
+      <c r="P8" s="95" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q8" s="96"/>
     </row>
     <row r="9" spans="2:17">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="58" t="s">
-        <v>86</v>
+      <c r="C9" s="103" t="s">
+        <v>83</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E9" s="4"/>
       <c r="G9" s="18">
         <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I9" s="2">
         <v>123</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K9" s="2">
         <v>-1</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="N9" s="39"/>
       <c r="O9" s="40"/>
       <c r="P9" s="39" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q9" s="40"/>
     </row>
@@ -2527,36 +2522,36 @@
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="58"/>
+      <c r="C10" s="103"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G10" s="23">
         <v>3</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I10" s="2">
         <v>123</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="N10" s="39"/>
       <c r="O10" s="40"/>
       <c r="P10" s="39" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q10" s="40"/>
     </row>
@@ -2564,38 +2559,38 @@
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="55" t="s">
-        <v>88</v>
+      <c r="C11" s="100" t="s">
+        <v>85</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E11" s="4"/>
       <c r="G11" s="23">
         <v>4</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I11" s="2">
         <v>123</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="N11" s="39"/>
       <c r="O11" s="40"/>
       <c r="P11" s="41" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Q11" s="42"/>
     </row>
@@ -2603,36 +2598,36 @@
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="57"/>
+      <c r="C12" s="102"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G12" s="10">
         <v>5</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I12" s="2">
         <v>123</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K12" s="2">
         <v>1</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="N12" s="39"/>
       <c r="O12" s="40"/>
       <c r="P12" s="41" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Q12" s="42"/>
     </row>
@@ -2640,49 +2635,49 @@
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="55" t="s">
-        <v>113</v>
+      <c r="C13" s="100" t="s">
+        <v>110</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E13" s="4"/>
       <c r="G13" s="10">
         <v>6</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I13" s="2">
         <v>123</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K13" s="2">
         <v>1</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="N13" s="66"/>
-      <c r="O13" s="67"/>
-      <c r="P13" s="66" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q13" s="67"/>
+        <v>93</v>
+      </c>
+      <c r="N13" s="110"/>
+      <c r="O13" s="111"/>
+      <c r="P13" s="110" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q13" s="111"/>
     </row>
     <row r="14" spans="2:17">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="56"/>
+      <c r="C14" s="101"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G14" s="23">
         <v>7</v>
@@ -2692,10 +2687,10 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="57"/>
+      <c r="C15" s="102"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G15" s="14">
         <v>8</v>
@@ -2706,10 +2701,10 @@
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="69"/>
-      <c r="P15" s="77"/>
-      <c r="Q15" s="78"/>
+      <c r="N15" s="95"/>
+      <c r="O15" s="96"/>
+      <c r="P15" s="98"/>
+      <c r="Q15" s="99"/>
     </row>
     <row r="16" spans="2:17">
       <c r="B16" s="4">
@@ -2725,17 +2720,17 @@
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
       <c r="M16" s="13"/>
-      <c r="N16" s="68"/>
-      <c r="O16" s="69"/>
-      <c r="P16" s="77"/>
-      <c r="Q16" s="78"/>
+      <c r="N16" s="95"/>
+      <c r="O16" s="96"/>
+      <c r="P16" s="98"/>
+      <c r="Q16" s="99"/>
     </row>
     <row r="17" spans="2:17">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="58" t="s">
-        <v>35</v>
+      <c r="C17" s="103" t="s">
+        <v>32</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -2746,16 +2741,16 @@
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
-      <c r="N17" s="68"/>
-      <c r="O17" s="69"/>
-      <c r="P17" s="77"/>
-      <c r="Q17" s="78"/>
+      <c r="N17" s="95"/>
+      <c r="O17" s="96"/>
+      <c r="P17" s="98"/>
+      <c r="Q17" s="99"/>
     </row>
     <row r="18" spans="2:17">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="58"/>
+      <c r="C18" s="103"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="G18" s="14"/>
@@ -2765,17 +2760,17 @@
       <c r="K18" s="13"/>
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
-      <c r="N18" s="68"/>
-      <c r="O18" s="69"/>
-      <c r="P18" s="77"/>
-      <c r="Q18" s="78"/>
+      <c r="N18" s="95"/>
+      <c r="O18" s="96"/>
+      <c r="P18" s="98"/>
+      <c r="Q18" s="99"/>
     </row>
     <row r="19" spans="2:17">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="58" t="s">
-        <v>35</v>
+      <c r="C19" s="103" t="s">
+        <v>32</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -2786,43 +2781,28 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="68"/>
-      <c r="O19" s="69"/>
-      <c r="P19" s="77"/>
-      <c r="Q19" s="78"/>
+      <c r="N19" s="95"/>
+      <c r="O19" s="96"/>
+      <c r="P19" s="98"/>
+      <c r="Q19" s="99"/>
     </row>
     <row r="20" spans="2:17">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="58"/>
+      <c r="C20" s="103"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
     <row r="22" spans="2:17">
       <c r="D22" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" s="76"/>
-      <c r="G22" s="76"/>
+        <v>37</v>
+      </c>
+      <c r="F22" s="97"/>
+      <c r="G22" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P15:Q15"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="C19:C20"/>
@@ -2839,13 +2819,28 @@
     <mergeCell ref="P8:Q8"/>
     <mergeCell ref="N7:O7"/>
     <mergeCell ref="H6:H7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P15:Q15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
@@ -2871,121 +2866,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18">
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="53"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="87"/>
     </row>
     <row r="3" spans="2:18">
-      <c r="B3" s="59" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="61"/>
+      <c r="B3" s="104" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="106"/>
     </row>
     <row r="5" spans="2:18">
-      <c r="B5" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
+      <c r="B5" s="119" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="63"/>
-      <c r="N5" s="63"/>
-      <c r="O5" s="63"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
+      <c r="G5" s="108" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="108"/>
+      <c r="M5" s="108"/>
+      <c r="N5" s="108"/>
+      <c r="O5" s="108"/>
+      <c r="P5" s="108"/>
+      <c r="Q5" s="108"/>
+      <c r="R5" s="108"/>
     </row>
     <row r="6" spans="2:18" ht="14.4" customHeight="1">
       <c r="B6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="G6" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="G6" s="64" t="s">
+      <c r="J6" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="64" t="s">
+      <c r="K6" s="115" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="116"/>
+      <c r="M6" s="116"/>
+      <c r="N6" s="116"/>
+      <c r="O6" s="116"/>
+      <c r="P6" s="117"/>
+      <c r="Q6" s="115" t="s">
+        <v>28</v>
+      </c>
+      <c r="R6" s="117"/>
+    </row>
+    <row r="7" spans="2:18">
+      <c r="B7" s="100">
+        <v>1</v>
+      </c>
+      <c r="C7" s="124" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="109"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="M7" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="N7" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="76" t="s">
         <v>45</v>
       </c>
-      <c r="I6" s="64" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" s="72" t="s">
-        <v>47</v>
-      </c>
-      <c r="K6" s="85" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="93"/>
-      <c r="M6" s="93"/>
-      <c r="N6" s="93"/>
-      <c r="O6" s="93"/>
-      <c r="P6" s="86"/>
-      <c r="Q6" s="85" t="s">
-        <v>31</v>
-      </c>
-      <c r="R6" s="86"/>
-    </row>
-    <row r="7" spans="2:18">
-      <c r="B7" s="55">
-        <v>1</v>
-      </c>
-      <c r="C7" s="79" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="65"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="L7" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="M7" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="N7" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O7" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="70" t="s">
-        <v>48</v>
-      </c>
-      <c r="R7" s="71"/>
+      <c r="R7" s="78"/>
     </row>
     <row r="8" spans="2:18">
-      <c r="B8" s="56"/>
-      <c r="C8" s="80"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="125"/>
       <c r="D8" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G8" s="18">
         <v>1</v>
@@ -2994,7 +2989,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J8" s="11"/>
       <c r="K8" s="22"/>
@@ -3003,14 +2998,14 @@
       <c r="N8" s="22"/>
       <c r="O8" s="22"/>
       <c r="P8" s="22"/>
-      <c r="Q8" s="87"/>
-      <c r="R8" s="88"/>
+      <c r="Q8" s="113"/>
+      <c r="R8" s="114"/>
     </row>
     <row r="9" spans="2:18">
-      <c r="B9" s="56"/>
-      <c r="C9" s="80"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="125"/>
       <c r="D9" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G9" s="14">
         <v>2</v>
@@ -3020,34 +3015,34 @@
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="16" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K9" s="2">
         <v>123</v>
       </c>
       <c r="L9" s="17" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M9" s="22">
         <v>7</v>
       </c>
       <c r="N9" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P9" s="13"/>
-      <c r="Q9" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="R9" s="92"/>
+      <c r="Q9" s="122" t="s">
+        <v>35</v>
+      </c>
+      <c r="R9" s="123"/>
     </row>
     <row r="10" spans="2:18">
-      <c r="B10" s="56"/>
-      <c r="C10" s="80"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="125"/>
       <c r="D10" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G10" s="18">
         <v>3</v>
@@ -3061,28 +3056,28 @@
         <v>123</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M10" s="22">
         <v>7</v>
       </c>
       <c r="N10" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P10" s="22"/>
-      <c r="Q10" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="R10" s="88"/>
+      <c r="Q10" s="113" t="s">
+        <v>31</v>
+      </c>
+      <c r="R10" s="114"/>
     </row>
     <row r="11" spans="2:18">
-      <c r="B11" s="56"/>
-      <c r="C11" s="80"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="125"/>
       <c r="D11" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G11" s="18">
         <v>4</v>
@@ -3096,28 +3091,28 @@
         <v>123</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M11" s="22">
         <v>7</v>
       </c>
       <c r="N11" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P11" s="22"/>
-      <c r="Q11" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="R11" s="88"/>
+      <c r="Q11" s="113" t="s">
+        <v>31</v>
+      </c>
+      <c r="R11" s="114"/>
     </row>
     <row r="12" spans="2:18">
-      <c r="B12" s="57"/>
-      <c r="C12" s="81"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="126"/>
       <c r="D12" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G12" s="18">
         <v>5</v>
@@ -3131,32 +3126,32 @@
         <v>123</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M12" s="22">
         <v>7</v>
       </c>
       <c r="N12" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P12" s="22"/>
-      <c r="Q12" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="R12" s="88"/>
+      <c r="Q12" s="113" t="s">
+        <v>31</v>
+      </c>
+      <c r="R12" s="114"/>
     </row>
     <row r="13" spans="2:18">
-      <c r="B13" s="55">
+      <c r="B13" s="100">
         <v>2</v>
       </c>
-      <c r="C13" s="79" t="s">
-        <v>88</v>
+      <c r="C13" s="124" t="s">
+        <v>85</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G13" s="14">
         <v>6</v>
@@ -3170,28 +3165,28 @@
         <v>123</v>
       </c>
       <c r="L13" s="45" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M13" s="22">
         <v>7</v>
       </c>
       <c r="N13" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P13" s="13"/>
-      <c r="Q13" s="66" t="s">
+      <c r="Q13" s="110" t="s">
+        <v>114</v>
+      </c>
+      <c r="R13" s="111"/>
+    </row>
+    <row r="14" spans="2:18">
+      <c r="B14" s="101"/>
+      <c r="C14" s="125"/>
+      <c r="D14" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="R13" s="67"/>
-    </row>
-    <row r="14" spans="2:18">
-      <c r="B14" s="56"/>
-      <c r="C14" s="80"/>
-      <c r="D14" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="G14" s="18">
         <v>7</v>
@@ -3200,7 +3195,7 @@
         <v>7</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J14" s="11"/>
       <c r="K14" s="22"/>
@@ -3209,14 +3204,14 @@
       <c r="N14" s="22"/>
       <c r="O14" s="22"/>
       <c r="P14" s="22"/>
-      <c r="Q14" s="87"/>
-      <c r="R14" s="88"/>
+      <c r="Q14" s="113"/>
+      <c r="R14" s="114"/>
     </row>
     <row r="15" spans="2:18">
-      <c r="B15" s="56"/>
-      <c r="C15" s="80"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="125"/>
       <c r="D15" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G15" s="18">
         <v>8</v>
@@ -3230,7 +3225,7 @@
         <v>123</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M15" s="22">
         <v>0</v>
@@ -3238,16 +3233,16 @@
       <c r="N15" s="22"/>
       <c r="O15" s="22"/>
       <c r="P15" s="22"/>
-      <c r="Q15" s="89" t="s">
-        <v>100</v>
-      </c>
-      <c r="R15" s="90"/>
+      <c r="Q15" s="120" t="s">
+        <v>97</v>
+      </c>
+      <c r="R15" s="121"/>
     </row>
     <row r="16" spans="2:18">
-      <c r="B16" s="56"/>
-      <c r="C16" s="80"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="125"/>
       <c r="D16" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G16" s="18">
         <v>9</v>
@@ -3256,7 +3251,7 @@
         <v>9</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J16" s="11"/>
       <c r="K16" s="22"/>
@@ -3265,16 +3260,16 @@
       <c r="N16" s="22"/>
       <c r="O16" s="22"/>
       <c r="P16" s="22"/>
-      <c r="Q16" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="R16" s="88"/>
+      <c r="Q16" s="113" t="s">
+        <v>31</v>
+      </c>
+      <c r="R16" s="114"/>
     </row>
     <row r="17" spans="2:18">
-      <c r="B17" s="56"/>
-      <c r="C17" s="80"/>
+      <c r="B17" s="101"/>
+      <c r="C17" s="125"/>
       <c r="D17" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G17" s="18">
         <v>10</v>
@@ -3287,28 +3282,28 @@
         <v>123</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="N17" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P17" s="22"/>
-      <c r="Q17" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="R17" s="88"/>
+      <c r="Q17" s="113" t="s">
+        <v>31</v>
+      </c>
+      <c r="R17" s="114"/>
     </row>
     <row r="18" spans="2:18">
-      <c r="B18" s="57"/>
-      <c r="C18" s="81"/>
+      <c r="B18" s="102"/>
+      <c r="C18" s="126"/>
       <c r="D18" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G18" s="18">
         <v>11</v>
@@ -3318,34 +3313,34 @@
       </c>
       <c r="I18" s="11"/>
       <c r="J18" s="16" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K18" s="22">
         <v>123</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M18" s="22" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="N18" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P18" s="22"/>
-      <c r="Q18" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="R18" s="92"/>
+      <c r="Q18" s="122" t="s">
+        <v>35</v>
+      </c>
+      <c r="R18" s="123"/>
     </row>
     <row r="19" spans="2:18">
-      <c r="B19" s="55">
+      <c r="B19" s="100">
         <v>3</v>
       </c>
-      <c r="C19" s="79"/>
+      <c r="C19" s="124"/>
       <c r="D19" s="2"/>
       <c r="G19" s="18">
         <v>12</v>
@@ -3359,26 +3354,26 @@
         <v>123</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M19" s="22" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="N19" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P19" s="22"/>
-      <c r="Q19" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="R19" s="88"/>
+      <c r="Q19" s="113" t="s">
+        <v>31</v>
+      </c>
+      <c r="R19" s="114"/>
     </row>
     <row r="20" spans="2:18">
-      <c r="B20" s="56"/>
-      <c r="C20" s="80"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="125"/>
       <c r="D20" s="2"/>
       <c r="G20" s="18">
         <v>13</v>
@@ -3392,12 +3387,12 @@
       <c r="N20" s="22"/>
       <c r="O20" s="22"/>
       <c r="P20" s="22"/>
-      <c r="Q20" s="87"/>
-      <c r="R20" s="88"/>
+      <c r="Q20" s="113"/>
+      <c r="R20" s="114"/>
     </row>
     <row r="21" spans="2:18">
-      <c r="B21" s="56"/>
-      <c r="C21" s="80"/>
+      <c r="B21" s="101"/>
+      <c r="C21" s="125"/>
       <c r="D21" s="2"/>
       <c r="G21" s="18">
         <v>14</v>
@@ -3411,12 +3406,12 @@
       <c r="N21" s="22"/>
       <c r="O21" s="22"/>
       <c r="P21" s="22"/>
-      <c r="Q21" s="87"/>
-      <c r="R21" s="88"/>
+      <c r="Q21" s="113"/>
+      <c r="R21" s="114"/>
     </row>
     <row r="22" spans="2:18">
-      <c r="B22" s="56"/>
-      <c r="C22" s="80"/>
+      <c r="B22" s="101"/>
+      <c r="C22" s="125"/>
       <c r="D22" s="2"/>
       <c r="G22" s="18">
         <v>15</v>
@@ -3430,12 +3425,12 @@
       <c r="N22" s="22"/>
       <c r="O22" s="22"/>
       <c r="P22" s="22"/>
-      <c r="Q22" s="87"/>
-      <c r="R22" s="88"/>
+      <c r="Q22" s="113"/>
+      <c r="R22" s="114"/>
     </row>
     <row r="23" spans="2:18">
-      <c r="B23" s="56"/>
-      <c r="C23" s="80"/>
+      <c r="B23" s="101"/>
+      <c r="C23" s="125"/>
       <c r="D23" s="2"/>
       <c r="G23" s="18">
         <v>16</v>
@@ -3449,12 +3444,12 @@
       <c r="N23" s="22"/>
       <c r="O23" s="22"/>
       <c r="P23" s="22"/>
-      <c r="Q23" s="87"/>
-      <c r="R23" s="88"/>
+      <c r="Q23" s="113"/>
+      <c r="R23" s="114"/>
     </row>
     <row r="24" spans="2:18">
-      <c r="B24" s="57"/>
-      <c r="C24" s="81"/>
+      <c r="B24" s="102"/>
+      <c r="C24" s="126"/>
       <c r="D24" s="2"/>
       <c r="G24" s="18">
         <v>17</v>
@@ -3468,25 +3463,25 @@
       <c r="N24" s="22"/>
       <c r="O24" s="22"/>
       <c r="P24" s="22"/>
-      <c r="Q24" s="87"/>
-      <c r="R24" s="88"/>
+      <c r="Q24" s="113"/>
+      <c r="R24" s="114"/>
     </row>
     <row r="25" spans="2:18">
-      <c r="B25" s="55">
+      <c r="B25" s="100">
         <v>4</v>
       </c>
-      <c r="C25" s="79" t="s">
-        <v>35</v>
+      <c r="C25" s="124" t="s">
+        <v>32</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G25" s="18">
         <v>18</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="22"/>
@@ -3495,68 +3490,76 @@
       <c r="N25" s="22"/>
       <c r="O25" s="22"/>
       <c r="P25" s="22"/>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="88"/>
+      <c r="Q25" s="113"/>
+      <c r="R25" s="114"/>
     </row>
     <row r="26" spans="2:18">
-      <c r="B26" s="56"/>
-      <c r="C26" s="80"/>
+      <c r="B26" s="101"/>
+      <c r="C26" s="125"/>
       <c r="D26" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="2:18">
-      <c r="B27" s="56"/>
-      <c r="C27" s="80"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="125"/>
       <c r="D27" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="2:18">
-      <c r="B28" s="56"/>
-      <c r="C28" s="80"/>
+      <c r="B28" s="101"/>
+      <c r="C28" s="125"/>
       <c r="D28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="83"/>
-      <c r="M28" s="83"/>
+        <v>32</v>
+      </c>
+      <c r="G28" s="97"/>
+      <c r="H28" s="97"/>
+      <c r="I28" s="118"/>
+      <c r="J28" s="118"/>
+      <c r="K28" s="118"/>
+      <c r="L28" s="118"/>
+      <c r="M28" s="118"/>
       <c r="N28" s="30"/>
     </row>
     <row r="29" spans="2:18">
-      <c r="B29" s="56"/>
-      <c r="C29" s="80"/>
+      <c r="B29" s="101"/>
+      <c r="C29" s="125"/>
       <c r="D29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I29" s="82"/>
-      <c r="J29" s="82"/>
-      <c r="K29" s="82"/>
-      <c r="L29" s="82"/>
-      <c r="M29" s="82"/>
+        <v>32</v>
+      </c>
+      <c r="I29" s="127"/>
+      <c r="J29" s="127"/>
+      <c r="K29" s="127"/>
+      <c r="L29" s="127"/>
+      <c r="M29" s="127"/>
       <c r="N29" s="31"/>
     </row>
     <row r="30" spans="2:18">
-      <c r="B30" s="57"/>
-      <c r="C30" s="81"/>
+      <c r="B30" s="102"/>
+      <c r="C30" s="126"/>
       <c r="D30" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="C7:C12"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C13:C18"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="I29:M29"/>
+    <mergeCell ref="G5:R5"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="Q7:R7"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="I28:M28"/>
     <mergeCell ref="B5:D5"/>
@@ -3573,22 +3576,14 @@
     <mergeCell ref="Q18:R18"/>
     <mergeCell ref="Q8:R8"/>
     <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="B7:B12"/>
-    <mergeCell ref="C7:C12"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="C13:C18"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="I29:M29"/>
-    <mergeCell ref="G5:R5"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q12:R12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3597,7 +3592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
@@ -3615,121 +3610,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14">
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="53"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="87"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
+    </row>
+    <row r="4" spans="2:14">
+      <c r="B4" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="90" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="107"/>
-      <c r="K3" s="107"/>
-      <c r="L3" s="107"/>
-      <c r="M3" s="107"/>
-      <c r="N3" s="107"/>
-    </row>
-    <row r="4" spans="2:14">
-      <c r="B4" s="64" t="s">
+      <c r="E4" s="88" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="105" t="s">
+      <c r="F4" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="78"/>
+      <c r="M4" s="72" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" s="72"/>
+    </row>
+    <row r="5" spans="2:14">
+      <c r="B5" s="60"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="K5" s="73"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="43" t="s">
         <v>57</v>
-      </c>
-      <c r="D4" s="103" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="72" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="74" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="74"/>
-    </row>
-    <row r="5" spans="2:14">
-      <c r="B5" s="109"/>
-      <c r="C5" s="106"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="G5" s="43" t="s">
-        <v>90</v>
-      </c>
-      <c r="H5" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="I5" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="K5" s="102"/>
-      <c r="L5" s="103"/>
-      <c r="M5" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="N5" s="43" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="6" spans="2:14">
       <c r="B6" s="9">
         <v>1</v>
       </c>
-      <c r="C6" s="99" t="s">
-        <v>61</v>
+      <c r="C6" s="82" t="s">
+        <v>58</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F6" s="2">
         <v>123</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
       </c>
-      <c r="I6" s="48" t="s">
-        <v>95</v>
+      <c r="I6" s="46" t="s">
+        <v>92</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K6" s="94"/>
-      <c r="L6" s="94"/>
+        <v>93</v>
+      </c>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
       <c r="M6" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="2:14">
@@ -3737,35 +3732,35 @@
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="100"/>
+      <c r="C7" s="83"/>
       <c r="D7" s="18" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F7" s="2">
         <v>123</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H7" s="2">
         <v>-1</v>
       </c>
       <c r="I7" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K7" s="95"/>
-      <c r="L7" s="95"/>
-      <c r="M7" s="129" t="s">
-        <v>144</v>
+        <v>93</v>
+      </c>
+      <c r="K7" s="79"/>
+      <c r="L7" s="79"/>
+      <c r="M7" s="49" t="s">
+        <v>141</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="2:14">
@@ -3773,35 +3768,35 @@
         <f t="shared" ref="B8:B20" si="0">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="100"/>
+      <c r="C8" s="83"/>
       <c r="D8" s="18" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F8" s="2">
         <v>123</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
       </c>
       <c r="I8" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
-      <c r="M8" s="129" t="s">
-        <v>148</v>
+      <c r="M8" s="49" t="s">
+        <v>145</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="2:14">
@@ -3809,35 +3804,35 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="100"/>
+      <c r="C9" s="83"/>
       <c r="D9" s="18" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F9" s="2">
         <v>123</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I9" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K9" s="96"/>
-      <c r="L9" s="96"/>
+        <v>93</v>
+      </c>
+      <c r="K9" s="80"/>
+      <c r="L9" s="80"/>
       <c r="M9" s="9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="2:14">
@@ -3845,35 +3840,35 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C10" s="100"/>
+      <c r="C10" s="83"/>
       <c r="D10" s="18" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F10" s="2">
         <v>123</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K10" s="97"/>
-      <c r="L10" s="97"/>
-      <c r="M10" s="129" t="s">
-        <v>38</v>
+        <v>93</v>
+      </c>
+      <c r="K10" s="75"/>
+      <c r="L10" s="75"/>
+      <c r="M10" s="49" t="s">
+        <v>35</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="2:14">
@@ -3881,35 +3876,35 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C11" s="100"/>
+      <c r="C11" s="83"/>
       <c r="D11" s="18" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F11" s="2">
         <v>123</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K11" s="97"/>
-      <c r="L11" s="97"/>
+        <v>93</v>
+      </c>
+      <c r="K11" s="75"/>
+      <c r="L11" s="75"/>
       <c r="M11" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="2:14">
@@ -3917,35 +3912,35 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C12" s="100"/>
+      <c r="C12" s="83"/>
       <c r="D12" s="18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F12" s="2">
         <v>123</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H12" s="22">
         <v>7</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K12" s="97"/>
-      <c r="L12" s="97"/>
+        <v>93</v>
+      </c>
+      <c r="K12" s="75"/>
+      <c r="L12" s="75"/>
       <c r="M12" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="2:14">
@@ -3953,35 +3948,35 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C13" s="100"/>
+      <c r="C13" s="83"/>
       <c r="D13" s="18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F13" s="2">
         <v>123</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H13" s="22">
         <v>7</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" s="96"/>
-      <c r="L13" s="96"/>
-      <c r="M13" s="128" t="s">
-        <v>34</v>
+        <v>93</v>
+      </c>
+      <c r="K13" s="80"/>
+      <c r="L13" s="80"/>
+      <c r="M13" s="48" t="s">
+        <v>31</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="2:14">
@@ -3989,35 +3984,35 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C14" s="100"/>
+      <c r="C14" s="83"/>
       <c r="D14" s="18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F14" s="2">
         <v>123</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H14" s="22">
         <v>7</v>
       </c>
-      <c r="I14" s="48" t="s">
-        <v>95</v>
+      <c r="I14" s="46" t="s">
+        <v>92</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K14" s="94"/>
-      <c r="L14" s="94"/>
+        <v>93</v>
+      </c>
+      <c r="K14" s="74"/>
+      <c r="L14" s="74"/>
       <c r="M14" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="14.4" customHeight="1">
@@ -4025,35 +4020,35 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C15" s="100"/>
+      <c r="C15" s="83"/>
       <c r="D15" s="18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F15" s="2">
         <v>123</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H15" s="22">
         <v>7</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K15" s="95"/>
-      <c r="L15" s="95"/>
-      <c r="M15" s="129" t="s">
-        <v>34</v>
+        <v>93</v>
+      </c>
+      <c r="K15" s="79"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="49" t="s">
+        <v>31</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="2:14">
@@ -4061,35 +4056,35 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C16" s="100"/>
+      <c r="C16" s="83"/>
       <c r="D16" s="18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F16" s="2">
         <v>123</v>
       </c>
       <c r="G16" s="45" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H16" s="22">
         <v>7</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
-      <c r="M16" s="129" t="s">
-        <v>145</v>
+      <c r="M16" s="49" t="s">
+        <v>142</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="2:16">
@@ -4097,35 +4092,35 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C17" s="100"/>
+      <c r="C17" s="83"/>
       <c r="D17" s="18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F17" s="2">
         <v>123</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H17" s="22">
         <v>0</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K17" s="96"/>
-      <c r="L17" s="96"/>
-      <c r="M17" s="128" t="s">
-        <v>147</v>
+        <v>93</v>
+      </c>
+      <c r="K17" s="80"/>
+      <c r="L17" s="80"/>
+      <c r="M17" s="48" t="s">
+        <v>144</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="14.4" customHeight="1">
@@ -4133,35 +4128,35 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C18" s="100"/>
+      <c r="C18" s="83"/>
       <c r="D18" s="18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F18" s="2">
         <v>123</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I18" s="48" t="s">
-        <v>95</v>
+        <v>127</v>
+      </c>
+      <c r="I18" s="46" t="s">
+        <v>92</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K18" s="97"/>
-      <c r="L18" s="97"/>
-      <c r="M18" s="129" t="s">
-        <v>38</v>
+        <v>93</v>
+      </c>
+      <c r="K18" s="75"/>
+      <c r="L18" s="75"/>
+      <c r="M18" s="49" t="s">
+        <v>35</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="2:16">
@@ -4169,35 +4164,35 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C19" s="100"/>
+      <c r="C19" s="83"/>
       <c r="D19" s="18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F19" s="2">
         <v>123</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I19" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K19" s="97"/>
-      <c r="L19" s="97"/>
+        <v>93</v>
+      </c>
+      <c r="K19" s="75"/>
+      <c r="L19" s="75"/>
       <c r="M19" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="2:16">
@@ -4205,55 +4200,55 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C20" s="101"/>
+      <c r="C20" s="84"/>
       <c r="D20" s="18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F20" s="2">
         <v>123</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I20" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K20" s="97"/>
-      <c r="L20" s="97"/>
+        <v>93</v>
+      </c>
+      <c r="K20" s="75"/>
+      <c r="L20" s="75"/>
       <c r="M20" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="2:16">
-      <c r="B21" s="46"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="46"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="81"/>
+      <c r="L21" s="81"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" s="19" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="20"/>
@@ -4263,102 +4258,102 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
-      <c r="K23" s="108"/>
-      <c r="L23" s="108"/>
+      <c r="K23" s="58"/>
+      <c r="L23" s="58"/>
       <c r="M23" s="7"/>
     </row>
     <row r="24" spans="2:16" ht="15" thickBot="1">
       <c r="M24" s="7"/>
     </row>
     <row r="25" spans="2:16" ht="15" thickTop="1">
-      <c r="C25" s="117" t="s">
+      <c r="C25" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="H25" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="I25" s="53"/>
+      <c r="J25" s="54"/>
+      <c r="K25" s="54"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="118"/>
-      <c r="E25" s="118"/>
-      <c r="F25" s="119"/>
-      <c r="G25" s="26" t="s">
+      <c r="N25" s="53"/>
+      <c r="O25" s="54"/>
+      <c r="P25" s="55"/>
+    </row>
+    <row r="26" spans="2:16">
+      <c r="B26" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="H25" s="117" t="s">
+      <c r="D26" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="I25" s="120"/>
-      <c r="J25" s="118"/>
-      <c r="K25" s="118"/>
-      <c r="L25" s="119"/>
-      <c r="M25" s="117" t="s">
+      <c r="E26" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="N25" s="120"/>
-      <c r="O25" s="118"/>
-      <c r="P25" s="119"/>
-    </row>
-    <row r="26" spans="2:16">
-      <c r="B26" s="113" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="114" t="s">
+      <c r="F26" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="D26" s="115" t="s">
+      <c r="G26" s="71" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="115" t="s">
+      <c r="H26" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="F26" s="116" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" s="125" t="s">
-        <v>77</v>
-      </c>
-      <c r="H26" s="121" t="s">
-        <v>78</v>
-      </c>
-      <c r="I26" s="122"/>
-      <c r="J26" s="115" t="s">
-        <v>73</v>
-      </c>
-      <c r="K26" s="115" t="s">
-        <v>74</v>
-      </c>
-      <c r="L26" s="116" t="s">
+      <c r="I26" s="68"/>
+      <c r="J26" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="K26" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="L26" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="M26" s="56" t="s">
         <v>75</v>
       </c>
-      <c r="M26" s="126" t="s">
-        <v>78</v>
-      </c>
-      <c r="N26" s="115" t="s">
-        <v>73</v>
-      </c>
-      <c r="O26" s="115" t="s">
-        <v>74</v>
-      </c>
-      <c r="P26" s="116" t="s">
-        <v>75</v>
+      <c r="N26" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="O26" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="P26" s="51" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="2:16">
-      <c r="B27" s="113"/>
-      <c r="C27" s="114"/>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="125"/>
-      <c r="H27" s="123"/>
-      <c r="I27" s="124"/>
-      <c r="J27" s="115"/>
-      <c r="K27" s="115"/>
-      <c r="L27" s="116"/>
-      <c r="M27" s="127"/>
-      <c r="N27" s="115"/>
-      <c r="O27" s="115"/>
-      <c r="P27" s="116"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="66"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="50"/>
+      <c r="L27" s="51"/>
+      <c r="M27" s="57"/>
+      <c r="N27" s="50"/>
+      <c r="O27" s="50"/>
+      <c r="P27" s="51"/>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" s="29" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C28" s="25">
         <v>15</v>
@@ -4367,15 +4362,15 @@
       <c r="E28" s="27"/>
       <c r="F28" s="28"/>
       <c r="G28" s="33"/>
-      <c r="H28" s="111" t="s">
-        <v>79</v>
-      </c>
-      <c r="I28" s="112"/>
+      <c r="H28" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="I28" s="64"/>
       <c r="J28" s="2"/>
       <c r="K28" s="27"/>
       <c r="L28" s="28"/>
       <c r="M28" s="32" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="27"/>
@@ -4383,11 +4378,28 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="M25:P25"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="C6:C20"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K9:L9"/>
     <mergeCell ref="K23:L23"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="D4:D5"/>
@@ -4404,28 +4416,11 @@
     <mergeCell ref="G26:G27"/>
     <mergeCell ref="K26:K27"/>
     <mergeCell ref="L26:L27"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="C6:C20"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="N26:N27"/>
   </mergeCells>
   <phoneticPr fontId="29" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4435,6 +4430,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="798a38e6de461387c626d04793181ea9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="301f98df-4edd-4096-94f8-2f8af3eee570" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b4b8dab68acb31e3ac71f6347d499c29" ns2:_="">
     <xsd:import namespace="301f98df-4edd-4096-94f8-2f8af3eee570"/>
@@ -4572,35 +4582,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E854E7-906F-4C7C-AFC0-1BC802AE88F0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4622,9 +4607,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E854E7-906F-4C7C-AFC0-1BC802AE88F0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/docs/lab2/Lab02_BBT_TCs_Form (1).xlsx
+++ b/docs/lab2/Lab02_BBT_TCs_Form (1).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="4788" yWindow="1056" windowWidth="17280" windowHeight="8880" tabRatio="522" activeTab="3"/>
+    <workbookView xWindow="4788" yWindow="1056" windowWidth="17280" windowHeight="8880" tabRatio="522"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -202,7 +202,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="148">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -240,43 +240,12 @@
     <t>Informaţiile vor fi preluate din fişiere text.</t>
   </si>
   <si>
-    <t>1. Evidenţa filmelor din colecţia personală</t>
-  </si>
-  <si>
-    <t>Un cinefil doreşte să îşi dezvolte un program pentru gestionarea filmelor din colecţia personală. Programul va permite următoarele operaţii:</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>F01.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> adăugarea unui film nou (titlu, regizor, an aparitie, actori, categorie, cuvinte cheie);</t>
-    </r>
-  </si>
-  <si>
     <t>Observații</t>
   </si>
   <si>
     <t xml:space="preserve">1. La proiectarea TCs se consideră o metodă care poate avea următoarea semnătură: </t>
   </si>
   <si>
-    <t>addMovie(String title, String director, int year, List&lt;String&gt; actors, String category, List&lt;String&gt; keywords): void</t>
-  </si>
-  <si>
     <t>2. Metoda este definită la nivelul repository, service sau ui.</t>
   </si>
   <si>
@@ -284,95 +253,6 @@
   </si>
   <si>
     <t>4. Pentru aceşti parametri se aplică ECP şi BVA. La proiectarea testelor se consideră că parametrii de intrare neinvestigaţi aici au valori valide, adică folosim dummy objects.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Exemplu: Parametrii </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>title</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> şi </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>year</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">; Condiţii pentru aceşti parametri de intrare: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>title</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> este un string cu lungimea validă de la 1 la 255 caractere; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>year</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="30"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> este valid dacă ia valori între 1899 şi 2025.</t>
-    </r>
   </si>
   <si>
     <t>EC Identification</t>
@@ -798,12 +678,36 @@
   <si>
     <t>Error message-? Invalid name</t>
   </si>
+  <si>
+    <t>addProduct(id, nume, pret,categorie,tip): void</t>
+  </si>
+  <si>
+    <t>Gestiunea bauturilor</t>
+  </si>
+  <si>
+    <r>
+      <t>Exemplu: Parametrii nume, pret</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color indexed="30"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>; Condiţii pentru aceşti parametri de intrare: nume este un string cu lungimea validă de la 1 la 255 caractere;</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Evidenţa bauturilor din magazin</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -847,14 +751,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color indexed="30"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
       <sz val="11"/>
       <color indexed="30"/>
       <name val="Calibri"/>
@@ -1432,7 +1328,7 @@
   </cellStyleXfs>
   <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1440,56 +1336,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1497,143 +1393,180 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1645,148 +1578,111 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2105,12 +2001,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10">
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="53"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="55"/>
       <c r="H1" s="38" t="s">
         <v>1</v>
       </c>
@@ -2118,11 +2014,11 @@
       <c r="J1" s="38"/>
     </row>
     <row r="2" spans="2:10">
-      <c r="H2" s="54" t="s">
+      <c r="H2" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="3" spans="2:10">
       <c r="H3" s="2"/>
@@ -2138,7 +2034,7 @@
         <v>5</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J4" s="2">
         <v>236</v>
@@ -2149,7 +2045,7 @@
         <v>6</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J5" s="2">
         <v>236</v>
@@ -2161,7 +2057,7 @@
         <v>7</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="J6" s="2">
         <v>236</v>
@@ -2202,7 +2098,7 @@
     </row>
     <row r="14" spans="2:10">
       <c r="B14" t="s">
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -2210,16 +2106,13 @@
     </row>
     <row r="15" spans="2:10">
       <c r="B15" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" t="s">
-        <v>14</v>
-      </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -2231,27 +2124,27 @@
     </row>
     <row r="18" spans="1:15">
       <c r="B18" s="36" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="B19" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="C20" s="34" t="s">
-        <v>17</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="B21" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="B22" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -2268,7 +2161,7 @@
     </row>
     <row r="23" spans="1:15">
       <c r="B23" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -2285,21 +2178,21 @@
     </row>
     <row r="24" spans="1:15" ht="14.4" customHeight="1">
       <c r="A24" s="35"/>
-      <c r="B24" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="50"/>
-      <c r="M24" s="50"/>
-      <c r="N24" s="50"/>
+      <c r="B24" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="52"/>
     </row>
     <row r="26" spans="1:15">
       <c r="C26" s="37"/>
@@ -2341,185 +2234,185 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17">
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="53"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="3" spans="2:17">
-      <c r="B3" s="59" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="61"/>
+      <c r="B3" s="70" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="72"/>
     </row>
     <row r="5" spans="2:17">
-      <c r="B5" s="62" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="G5" s="63" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="63"/>
-      <c r="N5" s="63"/>
-      <c r="O5" s="63"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
+      <c r="B5" s="73" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="G5" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="74"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
     </row>
     <row r="6" spans="2:17">
       <c r="B6" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="I6" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="60"/>
+      <c r="P6" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="72" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="75"/>
-      <c r="K6" s="75"/>
-      <c r="L6" s="75"/>
-      <c r="M6" s="75"/>
-      <c r="N6" s="75"/>
-      <c r="O6" s="71"/>
-      <c r="P6" s="74" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q6" s="74"/>
+      <c r="Q6" s="57"/>
     </row>
     <row r="7" spans="2:17">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="58" t="s">
-        <v>84</v>
+      <c r="C7" s="69" t="s">
+        <v>79</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="73"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="80"/>
       <c r="I7" s="18" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="M7" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="N7" s="70"/>
-      <c r="O7" s="71"/>
-      <c r="P7" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q7" s="71"/>
+        <v>88</v>
+      </c>
+      <c r="N7" s="58"/>
+      <c r="O7" s="60"/>
+      <c r="P7" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q7" s="60"/>
     </row>
     <row r="8" spans="2:17">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="58"/>
+      <c r="C8" s="69"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G8" s="18">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="I8" s="2">
         <v>123</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K8" s="2">
         <v>1</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="N8" s="68"/>
-      <c r="O8" s="69"/>
-      <c r="P8" s="68" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q8" s="69"/>
+        <v>91</v>
+      </c>
+      <c r="N8" s="61"/>
+      <c r="O8" s="62"/>
+      <c r="P8" s="61" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q8" s="62"/>
     </row>
     <row r="9" spans="2:17">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="58" t="s">
-        <v>86</v>
+      <c r="C9" s="69" t="s">
+        <v>81</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E9" s="4"/>
       <c r="G9" s="18">
         <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I9" s="2">
         <v>123</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K9" s="2">
         <v>-1</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="N9" s="39"/>
       <c r="O9" s="40"/>
       <c r="P9" s="39" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q9" s="40"/>
     </row>
@@ -2527,36 +2420,36 @@
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="58"/>
+      <c r="C10" s="69"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G10" s="23">
         <v>3</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I10" s="2">
         <v>123</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="N10" s="39"/>
       <c r="O10" s="40"/>
       <c r="P10" s="39" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="Q10" s="40"/>
     </row>
@@ -2564,38 +2457,38 @@
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="55" t="s">
-        <v>88</v>
+      <c r="C11" s="66" t="s">
+        <v>83</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E11" s="4"/>
       <c r="G11" s="23">
         <v>4</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="I11" s="2">
         <v>123</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="N11" s="39"/>
       <c r="O11" s="40"/>
       <c r="P11" s="41" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="Q11" s="42"/>
     </row>
@@ -2603,36 +2496,36 @@
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="57"/>
+      <c r="C12" s="68"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G12" s="10">
         <v>5</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I12" s="2">
         <v>123</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K12" s="2">
         <v>1</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="N12" s="39"/>
       <c r="O12" s="40"/>
       <c r="P12" s="41" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="Q12" s="42"/>
     </row>
@@ -2640,49 +2533,49 @@
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="55" t="s">
-        <v>113</v>
+      <c r="C13" s="66" t="s">
+        <v>108</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E13" s="4"/>
       <c r="G13" s="10">
         <v>6</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I13" s="2">
         <v>123</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="K13" s="2">
         <v>1</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="N13" s="66"/>
-      <c r="O13" s="67"/>
-      <c r="P13" s="66" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q13" s="67"/>
+        <v>91</v>
+      </c>
+      <c r="N13" s="77"/>
+      <c r="O13" s="78"/>
+      <c r="P13" s="77" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q13" s="78"/>
     </row>
     <row r="14" spans="2:17">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="56"/>
+      <c r="C14" s="67"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G14" s="23">
         <v>7</v>
@@ -2692,10 +2585,10 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="57"/>
+      <c r="C15" s="68"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G15" s="14">
         <v>8</v>
@@ -2706,10 +2599,10 @@
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="69"/>
-      <c r="P15" s="77"/>
-      <c r="Q15" s="78"/>
+      <c r="N15" s="61"/>
+      <c r="O15" s="62"/>
+      <c r="P15" s="64"/>
+      <c r="Q15" s="65"/>
     </row>
     <row r="16" spans="2:17">
       <c r="B16" s="4">
@@ -2725,17 +2618,17 @@
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
       <c r="M16" s="13"/>
-      <c r="N16" s="68"/>
-      <c r="O16" s="69"/>
-      <c r="P16" s="77"/>
-      <c r="Q16" s="78"/>
+      <c r="N16" s="61"/>
+      <c r="O16" s="62"/>
+      <c r="P16" s="64"/>
+      <c r="Q16" s="65"/>
     </row>
     <row r="17" spans="2:17">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="58" t="s">
-        <v>35</v>
+      <c r="C17" s="69" t="s">
+        <v>30</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -2746,16 +2639,16 @@
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
-      <c r="N17" s="68"/>
-      <c r="O17" s="69"/>
-      <c r="P17" s="77"/>
-      <c r="Q17" s="78"/>
+      <c r="N17" s="61"/>
+      <c r="O17" s="62"/>
+      <c r="P17" s="64"/>
+      <c r="Q17" s="65"/>
     </row>
     <row r="18" spans="2:17">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="58"/>
+      <c r="C18" s="69"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="G18" s="14"/>
@@ -2765,17 +2658,17 @@
       <c r="K18" s="13"/>
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
-      <c r="N18" s="68"/>
-      <c r="O18" s="69"/>
-      <c r="P18" s="77"/>
-      <c r="Q18" s="78"/>
+      <c r="N18" s="61"/>
+      <c r="O18" s="62"/>
+      <c r="P18" s="64"/>
+      <c r="Q18" s="65"/>
     </row>
     <row r="19" spans="2:17">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="58" t="s">
-        <v>35</v>
+      <c r="C19" s="69" t="s">
+        <v>30</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -2786,43 +2679,28 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="68"/>
-      <c r="O19" s="69"/>
-      <c r="P19" s="77"/>
-      <c r="Q19" s="78"/>
+      <c r="N19" s="61"/>
+      <c r="O19" s="62"/>
+      <c r="P19" s="64"/>
+      <c r="Q19" s="65"/>
     </row>
     <row r="20" spans="2:17">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="58"/>
+      <c r="C20" s="69"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
     <row r="22" spans="2:17">
       <c r="D22" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" s="76"/>
-      <c r="G22" s="76"/>
+        <v>35</v>
+      </c>
+      <c r="F22" s="63"/>
+      <c r="G22" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P15:Q15"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="C19:C20"/>
@@ -2839,6 +2717,21 @@
     <mergeCell ref="P8:Q8"/>
     <mergeCell ref="N7:O7"/>
     <mergeCell ref="H6:H7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P15:Q15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2871,121 +2764,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18">
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="53"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="3" spans="2:18">
-      <c r="B3" s="59" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="61"/>
+      <c r="B3" s="70" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="72"/>
     </row>
     <row r="5" spans="2:18">
-      <c r="B5" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
+      <c r="B5" s="87" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="63"/>
-      <c r="N5" s="63"/>
-      <c r="O5" s="63"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
+      <c r="G5" s="74" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="74"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
     </row>
     <row r="6" spans="2:18" ht="14.4" customHeight="1">
       <c r="B6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="G6" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="79" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="84"/>
+      <c r="M6" s="84"/>
+      <c r="N6" s="84"/>
+      <c r="O6" s="84"/>
+      <c r="P6" s="85"/>
+      <c r="Q6" s="83" t="s">
+        <v>26</v>
+      </c>
+      <c r="R6" s="85"/>
+    </row>
+    <row r="7" spans="2:18">
+      <c r="B7" s="66">
+        <v>1</v>
+      </c>
+      <c r="C7" s="92" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" s="76"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="M7" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="N7" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="G6" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="I6" s="64" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" s="72" t="s">
-        <v>47</v>
-      </c>
-      <c r="K6" s="85" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="93"/>
-      <c r="M6" s="93"/>
-      <c r="N6" s="93"/>
-      <c r="O6" s="93"/>
-      <c r="P6" s="86"/>
-      <c r="Q6" s="85" t="s">
-        <v>31</v>
-      </c>
-      <c r="R6" s="86"/>
-    </row>
-    <row r="7" spans="2:18">
-      <c r="B7" s="55">
-        <v>1</v>
-      </c>
-      <c r="C7" s="79" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="65"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="L7" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="M7" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="N7" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O7" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="70" t="s">
-        <v>48</v>
-      </c>
-      <c r="R7" s="71"/>
+      <c r="R7" s="60"/>
     </row>
     <row r="8" spans="2:18">
-      <c r="B8" s="56"/>
-      <c r="C8" s="80"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="93"/>
       <c r="D8" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G8" s="18">
         <v>1</v>
@@ -2994,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J8" s="11"/>
       <c r="K8" s="22"/>
@@ -3003,14 +2896,14 @@
       <c r="N8" s="22"/>
       <c r="O8" s="22"/>
       <c r="P8" s="22"/>
-      <c r="Q8" s="87"/>
-      <c r="R8" s="88"/>
+      <c r="Q8" s="81"/>
+      <c r="R8" s="82"/>
     </row>
     <row r="9" spans="2:18">
-      <c r="B9" s="56"/>
-      <c r="C9" s="80"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="93"/>
       <c r="D9" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G9" s="14">
         <v>2</v>
@@ -3020,34 +2913,34 @@
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="16" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K9" s="2">
         <v>123</v>
       </c>
       <c r="L9" s="17" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="M9" s="22">
         <v>7</v>
       </c>
       <c r="N9" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P9" s="13"/>
-      <c r="Q9" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="R9" s="92"/>
+      <c r="Q9" s="90" t="s">
+        <v>33</v>
+      </c>
+      <c r="R9" s="91"/>
     </row>
     <row r="10" spans="2:18">
-      <c r="B10" s="56"/>
-      <c r="C10" s="80"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="93"/>
       <c r="D10" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G10" s="18">
         <v>3</v>
@@ -3061,28 +2954,28 @@
         <v>123</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M10" s="22">
         <v>7</v>
       </c>
       <c r="N10" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P10" s="22"/>
-      <c r="Q10" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="R10" s="88"/>
+      <c r="Q10" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="R10" s="82"/>
     </row>
     <row r="11" spans="2:18">
-      <c r="B11" s="56"/>
-      <c r="C11" s="80"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="93"/>
       <c r="D11" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G11" s="18">
         <v>4</v>
@@ -3096,28 +2989,28 @@
         <v>123</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M11" s="22">
         <v>7</v>
       </c>
       <c r="N11" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P11" s="22"/>
-      <c r="Q11" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="R11" s="88"/>
+      <c r="Q11" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="R11" s="82"/>
     </row>
     <row r="12" spans="2:18">
-      <c r="B12" s="57"/>
-      <c r="C12" s="81"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="94"/>
       <c r="D12" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G12" s="18">
         <v>5</v>
@@ -3131,32 +3024,32 @@
         <v>123</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M12" s="22">
         <v>7</v>
       </c>
       <c r="N12" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P12" s="22"/>
-      <c r="Q12" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="R12" s="88"/>
+      <c r="Q12" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="R12" s="82"/>
     </row>
     <row r="13" spans="2:18">
-      <c r="B13" s="55">
+      <c r="B13" s="66">
         <v>2</v>
       </c>
-      <c r="C13" s="79" t="s">
-        <v>88</v>
+      <c r="C13" s="92" t="s">
+        <v>83</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G13" s="14">
         <v>6</v>
@@ -3170,28 +3063,28 @@
         <v>123</v>
       </c>
       <c r="L13" s="45" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="M13" s="22">
         <v>7</v>
       </c>
       <c r="N13" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P13" s="13"/>
-      <c r="Q13" s="66" t="s">
-        <v>117</v>
-      </c>
-      <c r="R13" s="67"/>
+      <c r="Q13" s="77" t="s">
+        <v>112</v>
+      </c>
+      <c r="R13" s="78"/>
     </row>
     <row r="14" spans="2:18">
-      <c r="B14" s="56"/>
-      <c r="C14" s="80"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="93"/>
       <c r="D14" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G14" s="18">
         <v>7</v>
@@ -3200,7 +3093,7 @@
         <v>7</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="J14" s="11"/>
       <c r="K14" s="22"/>
@@ -3209,14 +3102,14 @@
       <c r="N14" s="22"/>
       <c r="O14" s="22"/>
       <c r="P14" s="22"/>
-      <c r="Q14" s="87"/>
-      <c r="R14" s="88"/>
+      <c r="Q14" s="81"/>
+      <c r="R14" s="82"/>
     </row>
     <row r="15" spans="2:18">
-      <c r="B15" s="56"/>
-      <c r="C15" s="80"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="93"/>
       <c r="D15" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G15" s="18">
         <v>8</v>
@@ -3230,7 +3123,7 @@
         <v>123</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M15" s="22">
         <v>0</v>
@@ -3238,16 +3131,16 @@
       <c r="N15" s="22"/>
       <c r="O15" s="22"/>
       <c r="P15" s="22"/>
-      <c r="Q15" s="89" t="s">
-        <v>100</v>
-      </c>
-      <c r="R15" s="90"/>
+      <c r="Q15" s="88" t="s">
+        <v>95</v>
+      </c>
+      <c r="R15" s="89"/>
     </row>
     <row r="16" spans="2:18">
-      <c r="B16" s="56"/>
-      <c r="C16" s="80"/>
+      <c r="B16" s="67"/>
+      <c r="C16" s="93"/>
       <c r="D16" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G16" s="18">
         <v>9</v>
@@ -3256,7 +3149,7 @@
         <v>9</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="J16" s="11"/>
       <c r="K16" s="22"/>
@@ -3265,16 +3158,16 @@
       <c r="N16" s="22"/>
       <c r="O16" s="22"/>
       <c r="P16" s="22"/>
-      <c r="Q16" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="R16" s="88"/>
+      <c r="Q16" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="R16" s="82"/>
     </row>
     <row r="17" spans="2:18">
-      <c r="B17" s="56"/>
-      <c r="C17" s="80"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="93"/>
       <c r="D17" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G17" s="18">
         <v>10</v>
@@ -3287,28 +3180,28 @@
         <v>123</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="N17" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P17" s="22"/>
-      <c r="Q17" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="R17" s="88"/>
+      <c r="Q17" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="R17" s="82"/>
     </row>
     <row r="18" spans="2:18">
-      <c r="B18" s="57"/>
-      <c r="C18" s="81"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="94"/>
       <c r="D18" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G18" s="18">
         <v>11</v>
@@ -3318,34 +3211,34 @@
       </c>
       <c r="I18" s="11"/>
       <c r="J18" s="16" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K18" s="22">
         <v>123</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M18" s="22" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="N18" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P18" s="22"/>
-      <c r="Q18" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="R18" s="92"/>
+      <c r="Q18" s="90" t="s">
+        <v>33</v>
+      </c>
+      <c r="R18" s="91"/>
     </row>
     <row r="19" spans="2:18">
-      <c r="B19" s="55">
+      <c r="B19" s="66">
         <v>3</v>
       </c>
-      <c r="C19" s="79"/>
+      <c r="C19" s="92"/>
       <c r="D19" s="2"/>
       <c r="G19" s="18">
         <v>12</v>
@@ -3359,26 +3252,26 @@
         <v>123</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M19" s="22" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="N19" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="P19" s="22"/>
-      <c r="Q19" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="R19" s="88"/>
+      <c r="Q19" s="81" t="s">
+        <v>29</v>
+      </c>
+      <c r="R19" s="82"/>
     </row>
     <row r="20" spans="2:18">
-      <c r="B20" s="56"/>
-      <c r="C20" s="80"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="93"/>
       <c r="D20" s="2"/>
       <c r="G20" s="18">
         <v>13</v>
@@ -3392,12 +3285,12 @@
       <c r="N20" s="22"/>
       <c r="O20" s="22"/>
       <c r="P20" s="22"/>
-      <c r="Q20" s="87"/>
-      <c r="R20" s="88"/>
+      <c r="Q20" s="81"/>
+      <c r="R20" s="82"/>
     </row>
     <row r="21" spans="2:18">
-      <c r="B21" s="56"/>
-      <c r="C21" s="80"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="93"/>
       <c r="D21" s="2"/>
       <c r="G21" s="18">
         <v>14</v>
@@ -3411,12 +3304,12 @@
       <c r="N21" s="22"/>
       <c r="O21" s="22"/>
       <c r="P21" s="22"/>
-      <c r="Q21" s="87"/>
-      <c r="R21" s="88"/>
+      <c r="Q21" s="81"/>
+      <c r="R21" s="82"/>
     </row>
     <row r="22" spans="2:18">
-      <c r="B22" s="56"/>
-      <c r="C22" s="80"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="93"/>
       <c r="D22" s="2"/>
       <c r="G22" s="18">
         <v>15</v>
@@ -3430,12 +3323,12 @@
       <c r="N22" s="22"/>
       <c r="O22" s="22"/>
       <c r="P22" s="22"/>
-      <c r="Q22" s="87"/>
-      <c r="R22" s="88"/>
+      <c r="Q22" s="81"/>
+      <c r="R22" s="82"/>
     </row>
     <row r="23" spans="2:18">
-      <c r="B23" s="56"/>
-      <c r="C23" s="80"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="93"/>
       <c r="D23" s="2"/>
       <c r="G23" s="18">
         <v>16</v>
@@ -3449,12 +3342,12 @@
       <c r="N23" s="22"/>
       <c r="O23" s="22"/>
       <c r="P23" s="22"/>
-      <c r="Q23" s="87"/>
-      <c r="R23" s="88"/>
+      <c r="Q23" s="81"/>
+      <c r="R23" s="82"/>
     </row>
     <row r="24" spans="2:18">
-      <c r="B24" s="57"/>
-      <c r="C24" s="81"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="94"/>
       <c r="D24" s="2"/>
       <c r="G24" s="18">
         <v>17</v>
@@ -3468,25 +3361,25 @@
       <c r="N24" s="22"/>
       <c r="O24" s="22"/>
       <c r="P24" s="22"/>
-      <c r="Q24" s="87"/>
-      <c r="R24" s="88"/>
+      <c r="Q24" s="81"/>
+      <c r="R24" s="82"/>
     </row>
     <row r="25" spans="2:18">
-      <c r="B25" s="55">
+      <c r="B25" s="66">
         <v>4</v>
       </c>
-      <c r="C25" s="79" t="s">
-        <v>35</v>
+      <c r="C25" s="92" t="s">
+        <v>30</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G25" s="18">
         <v>18</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="11" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="22"/>
@@ -3495,68 +3388,76 @@
       <c r="N25" s="22"/>
       <c r="O25" s="22"/>
       <c r="P25" s="22"/>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="88"/>
+      <c r="Q25" s="81"/>
+      <c r="R25" s="82"/>
     </row>
     <row r="26" spans="2:18">
-      <c r="B26" s="56"/>
-      <c r="C26" s="80"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="93"/>
       <c r="D26" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="2:18">
-      <c r="B27" s="56"/>
-      <c r="C27" s="80"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="93"/>
       <c r="D27" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="2:18">
-      <c r="B28" s="56"/>
-      <c r="C28" s="80"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="93"/>
       <c r="D28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="83"/>
-      <c r="M28" s="83"/>
+        <v>30</v>
+      </c>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="K28" s="86"/>
+      <c r="L28" s="86"/>
+      <c r="M28" s="86"/>
       <c r="N28" s="30"/>
     </row>
     <row r="29" spans="2:18">
-      <c r="B29" s="56"/>
-      <c r="C29" s="80"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="93"/>
       <c r="D29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I29" s="82"/>
-      <c r="J29" s="82"/>
-      <c r="K29" s="82"/>
-      <c r="L29" s="82"/>
-      <c r="M29" s="82"/>
+        <v>30</v>
+      </c>
+      <c r="I29" s="95"/>
+      <c r="J29" s="95"/>
+      <c r="K29" s="95"/>
+      <c r="L29" s="95"/>
+      <c r="M29" s="95"/>
       <c r="N29" s="31"/>
     </row>
     <row r="30" spans="2:18">
-      <c r="B30" s="57"/>
-      <c r="C30" s="81"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="94"/>
       <c r="D30" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="C7:C12"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C13:C18"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="I29:M29"/>
+    <mergeCell ref="G5:R5"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="Q7:R7"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="I28:M28"/>
     <mergeCell ref="B5:D5"/>
@@ -3573,22 +3474,14 @@
     <mergeCell ref="Q18:R18"/>
     <mergeCell ref="Q8:R8"/>
     <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="B7:B12"/>
-    <mergeCell ref="C7:C12"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="C13:C18"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="I29:M29"/>
-    <mergeCell ref="G5:R5"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q12:R12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3611,125 +3504,125 @@
     <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.88671875" customWidth="1"/>
     <col min="13" max="13" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.88671875" customWidth="1"/>
+    <col min="14" max="14" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:14">
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="53"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="129" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="N3" s="129"/>
+    </row>
+    <row r="4" spans="2:14">
+      <c r="B4" s="75" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="127" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="106" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="79" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="57"/>
+    </row>
+    <row r="5" spans="2:14">
+      <c r="B5" s="105"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="K5" s="117"/>
+      <c r="L5" s="106"/>
+      <c r="M5" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" s="43" t="s">
         <v>55</v>
-      </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="107"/>
-      <c r="K3" s="107"/>
-      <c r="L3" s="107"/>
-      <c r="M3" s="107"/>
-      <c r="N3" s="107"/>
-    </row>
-    <row r="4" spans="2:14">
-      <c r="B4" s="64" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="105" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="103" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="72" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="74" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="74"/>
-    </row>
-    <row r="5" spans="2:14">
-      <c r="B5" s="109"/>
-      <c r="C5" s="106"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="43" t="s">
-        <v>91</v>
-      </c>
-      <c r="G5" s="43" t="s">
-        <v>90</v>
-      </c>
-      <c r="H5" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="I5" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="K5" s="102"/>
-      <c r="L5" s="103"/>
-      <c r="M5" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="N5" s="43" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="6" spans="2:14">
       <c r="B6" s="9">
         <v>1</v>
       </c>
-      <c r="C6" s="99" t="s">
-        <v>61</v>
+      <c r="C6" s="123" t="s">
+        <v>56</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F6" s="2">
         <v>123</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
       </c>
       <c r="I6" s="48" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K6" s="94"/>
-      <c r="L6" s="94"/>
+        <v>91</v>
+      </c>
+      <c r="K6" s="118"/>
+      <c r="L6" s="118"/>
       <c r="M6" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="2:14">
@@ -3737,35 +3630,35 @@
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="100"/>
+      <c r="C7" s="124"/>
       <c r="D7" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>132</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>137</v>
       </c>
       <c r="F7" s="2">
         <v>123</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H7" s="2">
         <v>-1</v>
       </c>
       <c r="I7" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K7" s="95"/>
-      <c r="L7" s="95"/>
-      <c r="M7" s="129" t="s">
-        <v>144</v>
+        <v>91</v>
+      </c>
+      <c r="K7" s="120"/>
+      <c r="L7" s="120"/>
+      <c r="M7" s="51" t="s">
+        <v>139</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>35</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="2:14">
@@ -3773,35 +3666,35 @@
         <f t="shared" ref="B8:B20" si="0">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="100"/>
+      <c r="C8" s="124"/>
       <c r="D8" s="18" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F8" s="2">
         <v>123</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
       </c>
       <c r="I8" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
-      <c r="M8" s="129" t="s">
-        <v>148</v>
+      <c r="M8" s="51" t="s">
+        <v>143</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="2:14">
@@ -3809,35 +3702,35 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="100"/>
+      <c r="C9" s="124"/>
       <c r="D9" s="18" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F9" s="2">
         <v>123</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="I9" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K9" s="96"/>
-      <c r="L9" s="96"/>
+        <v>91</v>
+      </c>
+      <c r="K9" s="121"/>
+      <c r="L9" s="121"/>
       <c r="M9" s="9" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="2:14">
@@ -3845,35 +3738,35 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C10" s="100"/>
+      <c r="C10" s="124"/>
       <c r="D10" s="18" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F10" s="2">
         <v>123</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K10" s="97"/>
-      <c r="L10" s="97"/>
-      <c r="M10" s="129" t="s">
-        <v>38</v>
+        <v>91</v>
+      </c>
+      <c r="K10" s="119"/>
+      <c r="L10" s="119"/>
+      <c r="M10" s="51" t="s">
+        <v>33</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="2:14">
@@ -3881,35 +3774,35 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C11" s="100"/>
+      <c r="C11" s="124"/>
       <c r="D11" s="18" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F11" s="2">
         <v>123</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K11" s="97"/>
-      <c r="L11" s="97"/>
+        <v>91</v>
+      </c>
+      <c r="K11" s="119"/>
+      <c r="L11" s="119"/>
       <c r="M11" s="5" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>35</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="2:14">
@@ -3917,35 +3810,35 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C12" s="100"/>
+      <c r="C12" s="124"/>
       <c r="D12" s="18" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F12" s="2">
         <v>123</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H12" s="22">
         <v>7</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K12" s="97"/>
-      <c r="L12" s="97"/>
+        <v>91</v>
+      </c>
+      <c r="K12" s="119"/>
+      <c r="L12" s="119"/>
       <c r="M12" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="2:14">
@@ -3953,35 +3846,35 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C13" s="100"/>
+      <c r="C13" s="124"/>
       <c r="D13" s="18" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F13" s="2">
         <v>123</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H13" s="22">
         <v>7</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" s="96"/>
-      <c r="L13" s="96"/>
-      <c r="M13" s="128" t="s">
-        <v>34</v>
+        <v>91</v>
+      </c>
+      <c r="K13" s="121"/>
+      <c r="L13" s="121"/>
+      <c r="M13" s="50" t="s">
+        <v>29</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="2:14">
@@ -3989,35 +3882,35 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C14" s="100"/>
+      <c r="C14" s="124"/>
       <c r="D14" s="18" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F14" s="2">
         <v>123</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H14" s="22">
         <v>7</v>
       </c>
       <c r="I14" s="48" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K14" s="94"/>
-      <c r="L14" s="94"/>
+        <v>91</v>
+      </c>
+      <c r="K14" s="118"/>
+      <c r="L14" s="118"/>
       <c r="M14" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="14.4" customHeight="1">
@@ -4025,35 +3918,35 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C15" s="100"/>
+      <c r="C15" s="124"/>
       <c r="D15" s="18" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F15" s="2">
         <v>123</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H15" s="22">
         <v>7</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K15" s="95"/>
-      <c r="L15" s="95"/>
-      <c r="M15" s="129" t="s">
-        <v>34</v>
+        <v>91</v>
+      </c>
+      <c r="K15" s="120"/>
+      <c r="L15" s="120"/>
+      <c r="M15" s="51" t="s">
+        <v>29</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="2:14">
@@ -4061,35 +3954,35 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C16" s="100"/>
+      <c r="C16" s="124"/>
       <c r="D16" s="18" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F16" s="2">
         <v>123</v>
       </c>
       <c r="G16" s="45" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H16" s="22">
         <v>7</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
-      <c r="M16" s="129" t="s">
-        <v>145</v>
+      <c r="M16" s="51" t="s">
+        <v>140</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>35</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="2:16">
@@ -4097,35 +3990,35 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C17" s="100"/>
+      <c r="C17" s="124"/>
       <c r="D17" s="18" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F17" s="2">
         <v>123</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H17" s="22">
         <v>0</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K17" s="96"/>
-      <c r="L17" s="96"/>
-      <c r="M17" s="128" t="s">
-        <v>147</v>
+        <v>91</v>
+      </c>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="50" t="s">
+        <v>142</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>35</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="14.4" customHeight="1">
@@ -4133,35 +4026,35 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C18" s="100"/>
+      <c r="C18" s="124"/>
       <c r="D18" s="18" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F18" s="2">
         <v>123</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I18" s="48" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K18" s="97"/>
-      <c r="L18" s="97"/>
-      <c r="M18" s="129" t="s">
-        <v>38</v>
+        <v>91</v>
+      </c>
+      <c r="K18" s="119"/>
+      <c r="L18" s="119"/>
+      <c r="M18" s="51" t="s">
+        <v>33</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="2:16">
@@ -4169,35 +4062,35 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C19" s="100"/>
+      <c r="C19" s="124"/>
       <c r="D19" s="18" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F19" s="2">
         <v>123</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I19" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K19" s="97"/>
-      <c r="L19" s="97"/>
+        <v>91</v>
+      </c>
+      <c r="K19" s="119"/>
+      <c r="L19" s="119"/>
       <c r="M19" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="2:16">
@@ -4205,35 +4098,35 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C20" s="101"/>
+      <c r="C20" s="125"/>
       <c r="D20" s="18" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F20" s="2">
         <v>123</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I20" s="44" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K20" s="97"/>
-      <c r="L20" s="97"/>
+        <v>91</v>
+      </c>
+      <c r="K20" s="119"/>
+      <c r="L20" s="119"/>
       <c r="M20" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="2:16">
@@ -4246,14 +4139,14 @@
       <c r="H21" s="46"/>
       <c r="I21" s="46"/>
       <c r="J21" s="46"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="98"/>
+      <c r="K21" s="122"/>
+      <c r="L21" s="122"/>
       <c r="M21" s="46"/>
       <c r="N21" s="46"/>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" s="19" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="20"/>
@@ -4263,119 +4156,127 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
-      <c r="K23" s="108"/>
-      <c r="L23" s="108"/>
+      <c r="K23" s="104"/>
+      <c r="L23" s="104"/>
       <c r="M23" s="7"/>
     </row>
     <row r="24" spans="2:16" ht="15" thickBot="1">
       <c r="M24" s="7"/>
     </row>
     <row r="25" spans="2:16" ht="15" thickTop="1">
-      <c r="C25" s="117" t="s">
+      <c r="C25" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="100"/>
+      <c r="E25" s="100"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="H25" s="98" t="s">
+        <v>66</v>
+      </c>
+      <c r="I25" s="99"/>
+      <c r="J25" s="100"/>
+      <c r="K25" s="100"/>
+      <c r="L25" s="101"/>
+      <c r="M25" s="98" t="s">
+        <v>67</v>
+      </c>
+      <c r="N25" s="99"/>
+      <c r="O25" s="100"/>
+      <c r="P25" s="101"/>
+    </row>
+    <row r="26" spans="2:16">
+      <c r="B26" s="110" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="96" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="118"/>
-      <c r="E25" s="118"/>
-      <c r="F25" s="119"/>
-      <c r="G25" s="26" t="s">
+      <c r="E26" s="96" t="s">
         <v>70</v>
       </c>
-      <c r="H25" s="117" t="s">
+      <c r="F26" s="97" t="s">
         <v>71</v>
       </c>
-      <c r="I25" s="120"/>
-      <c r="J25" s="118"/>
-      <c r="K25" s="118"/>
-      <c r="L25" s="119"/>
-      <c r="M25" s="117" t="s">
+      <c r="G26" s="116" t="s">
         <v>72</v>
       </c>
-      <c r="N25" s="120"/>
-      <c r="O25" s="118"/>
-      <c r="P25" s="119"/>
-    </row>
-    <row r="26" spans="2:16">
-      <c r="B26" s="113" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="114" t="s">
+      <c r="H26" s="112" t="s">
         <v>73</v>
       </c>
-      <c r="D26" s="115" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26" s="115" t="s">
-        <v>75</v>
-      </c>
-      <c r="F26" s="116" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" s="125" t="s">
-        <v>77</v>
-      </c>
-      <c r="H26" s="121" t="s">
-        <v>78</v>
-      </c>
-      <c r="I26" s="122"/>
-      <c r="J26" s="115" t="s">
+      <c r="I26" s="113"/>
+      <c r="J26" s="96" t="s">
+        <v>68</v>
+      </c>
+      <c r="K26" s="96" t="s">
+        <v>69</v>
+      </c>
+      <c r="L26" s="97" t="s">
+        <v>70</v>
+      </c>
+      <c r="M26" s="102" t="s">
         <v>73</v>
       </c>
-      <c r="K26" s="115" t="s">
-        <v>74</v>
-      </c>
-      <c r="L26" s="116" t="s">
-        <v>75</v>
-      </c>
-      <c r="M26" s="126" t="s">
-        <v>78</v>
-      </c>
-      <c r="N26" s="115" t="s">
-        <v>73</v>
-      </c>
-      <c r="O26" s="115" t="s">
-        <v>74</v>
-      </c>
-      <c r="P26" s="116" t="s">
-        <v>75</v>
+      <c r="N26" s="96" t="s">
+        <v>68</v>
+      </c>
+      <c r="O26" s="96" t="s">
+        <v>69</v>
+      </c>
+      <c r="P26" s="97" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="2:16">
-      <c r="B27" s="113"/>
-      <c r="C27" s="114"/>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="125"/>
-      <c r="H27" s="123"/>
-      <c r="I27" s="124"/>
-      <c r="J27" s="115"/>
-      <c r="K27" s="115"/>
-      <c r="L27" s="116"/>
-      <c r="M27" s="127"/>
-      <c r="N27" s="115"/>
-      <c r="O27" s="115"/>
-      <c r="P27" s="116"/>
+      <c r="B27" s="110"/>
+      <c r="C27" s="111"/>
+      <c r="D27" s="96"/>
+      <c r="E27" s="96"/>
+      <c r="F27" s="97"/>
+      <c r="G27" s="116"/>
+      <c r="H27" s="114"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="96"/>
+      <c r="K27" s="96"/>
+      <c r="L27" s="97"/>
+      <c r="M27" s="103"/>
+      <c r="N27" s="96"/>
+      <c r="O27" s="96"/>
+      <c r="P27" s="97"/>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" s="29" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C28" s="25">
-        <v>15</v>
-      </c>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="111" t="s">
-        <v>79</v>
-      </c>
-      <c r="I28" s="112"/>
+        <v>11</v>
+      </c>
+      <c r="D28" s="27">
+        <v>11</v>
+      </c>
+      <c r="E28" s="27">
+        <v>0</v>
+      </c>
+      <c r="F28" s="28">
+        <v>0</v>
+      </c>
+      <c r="G28" s="33">
+        <v>0</v>
+      </c>
+      <c r="H28" s="108" t="s">
+        <v>74</v>
+      </c>
+      <c r="I28" s="109"/>
       <c r="J28" s="2"/>
       <c r="K28" s="27"/>
       <c r="L28" s="28"/>
       <c r="M28" s="32" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="27"/>
@@ -4383,11 +4284,28 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="M25:P25"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="C6:C20"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K9:L9"/>
     <mergeCell ref="K23:L23"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="D4:D5"/>
@@ -4404,30 +4322,13 @@
     <mergeCell ref="G26:G27"/>
     <mergeCell ref="K26:K27"/>
     <mergeCell ref="L26:L27"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="C6:C20"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="N26:N27"/>
   </mergeCells>
-  <phoneticPr fontId="29" type="noConversion"/>
+  <phoneticPr fontId="28" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -4435,6 +4336,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="798a38e6de461387c626d04793181ea9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="301f98df-4edd-4096-94f8-2f8af3eee570" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b4b8dab68acb31e3ac71f6347d499c29" ns2:_="">
     <xsd:import namespace="301f98df-4edd-4096-94f8-2f8af3eee570"/>
@@ -4572,35 +4488,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E854E7-906F-4C7C-AFC0-1BC802AE88F0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4622,9 +4513,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E854E7-906F-4C7C-AFC0-1BC802AE88F0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/docs/lab2/Lab02_BBT_TCs_Form (1).xlsx
+++ b/docs/lab2/Lab02_BBT_TCs_Form (1).xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40B5818-F9B5-4D75-A5AF-101ABC34D0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="522" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4788" yWindow="1056" windowWidth="17280" windowHeight="8880" tabRatio="522" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -13,7 +12,7 @@
     <sheet name="F01.BVA" sheetId="3" r:id="rId3"/>
     <sheet name="BBT-TCs" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,12 +33,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="D16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="D16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -64,7 +63,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="M17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -89,7 +88,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+    <comment ref="D22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -119,12 +118,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="H18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -149,7 +148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+    <comment ref="H26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -173,7 +172,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+    <comment ref="M26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -241,6 +240,12 @@
     <t>Informaţiile vor fi preluate din fişiere text.</t>
   </si>
   <si>
+    <t>1. Evidenţa filmelor din colecţia personală</t>
+  </si>
+  <si>
+    <t>Un cinefil doreşte să îşi dezvolte un program pentru gestionarea filmelor din colecţia personală. Programul va permite următoarele operaţii:</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -267,6 +272,9 @@
   </si>
   <si>
     <t xml:space="preserve">1. La proiectarea TCs se consideră o metodă care poate avea următoarea semnătură: </t>
+  </si>
+  <si>
+    <t>addMovie(String title, String director, int year, List&lt;String&gt; actors, String category, List&lt;String&gt; keywords): void</t>
   </si>
   <si>
     <t>2. Metoda este definită la nivelul repository, service sau ui.</t>
@@ -790,20 +798,11 @@
   <si>
     <t>Error message-? Invalid name</t>
   </si>
-  <si>
-    <t>addProduct ( id, nume, pret, categorie,tip): void;</t>
-  </si>
-  <si>
-    <t>1. Evidenţa bauturilor din magazin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gestiunea bauturilor </t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="30">
     <font>
       <sz val="11"/>
@@ -1431,7 +1430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1535,253 +1534,259 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1800,9 +1805,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1840,7 +1845,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1912,7 +1917,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2085,7 +2090,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
@@ -2100,12 +2105,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10">
-      <c r="C1" s="85" t="s">
+      <c r="C1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="87"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="53"/>
       <c r="H1" s="38" t="s">
         <v>1</v>
       </c>
@@ -2113,11 +2118,11 @@
       <c r="J1" s="38"/>
     </row>
     <row r="2" spans="2:10">
-      <c r="H2" s="94" t="s">
+      <c r="H2" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
     </row>
     <row r="3" spans="2:10">
       <c r="H3" s="2"/>
@@ -2133,7 +2138,7 @@
         <v>5</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J4" s="2">
         <v>236</v>
@@ -2144,7 +2149,7 @@
         <v>6</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J5" s="2">
         <v>236</v>
@@ -2156,7 +2161,7 @@
         <v>7</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J6" s="2">
         <v>236</v>
@@ -2197,7 +2202,7 @@
     </row>
     <row r="14" spans="2:10">
       <c r="B14" t="s">
-        <v>147</v>
+        <v>12</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -2205,7 +2210,7 @@
     </row>
     <row r="15" spans="2:10">
       <c r="B15" t="s">
-        <v>148</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -2213,7 +2218,7 @@
     </row>
     <row r="16" spans="2:10">
       <c r="B16" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -2226,27 +2231,27 @@
     </row>
     <row r="18" spans="1:15">
       <c r="B18" s="36" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="B19" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="C20" s="34" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="B22" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -2263,7 +2268,7 @@
     </row>
     <row r="23" spans="1:15">
       <c r="B23" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -2280,21 +2285,21 @@
     </row>
     <row r="24" spans="1:15" ht="14.4" customHeight="1">
       <c r="A24" s="35"/>
-      <c r="B24" s="93" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="93"/>
-      <c r="D24" s="93"/>
-      <c r="E24" s="93"/>
-      <c r="F24" s="93"/>
-      <c r="G24" s="93"/>
-      <c r="H24" s="93"/>
-      <c r="I24" s="93"/>
-      <c r="J24" s="93"/>
-      <c r="K24" s="93"/>
-      <c r="L24" s="93"/>
-      <c r="M24" s="93"/>
-      <c r="N24" s="93"/>
+      <c r="B24" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="50"/>
+      <c r="M24" s="50"/>
+      <c r="N24" s="50"/>
     </row>
     <row r="26" spans="1:15">
       <c r="C26" s="37"/>
@@ -2311,7 +2316,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
@@ -2336,185 +2341,185 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17">
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="53"/>
     </row>
     <row r="3" spans="2:17">
-      <c r="B3" s="104" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="106"/>
+      <c r="B3" s="59" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="61"/>
     </row>
     <row r="5" spans="2:17">
-      <c r="B5" s="107" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="107"/>
-      <c r="G5" s="108" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
-      <c r="L5" s="108"/>
-      <c r="M5" s="108"/>
-      <c r="N5" s="108"/>
-      <c r="O5" s="108"/>
-      <c r="P5" s="108"/>
-      <c r="Q5" s="108"/>
+      <c r="B5" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="G5" s="63" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
+      <c r="P5" s="63"/>
+      <c r="Q5" s="63"/>
     </row>
     <row r="6" spans="2:17">
       <c r="B6" s="18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="59" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="88" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="J6" s="77"/>
-      <c r="K6" s="77"/>
-      <c r="L6" s="77"/>
-      <c r="M6" s="77"/>
-      <c r="N6" s="77"/>
-      <c r="O6" s="78"/>
-      <c r="P6" s="72" t="s">
+      <c r="G6" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="Q6" s="72"/>
+      <c r="H6" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="75"/>
+      <c r="K6" s="75"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="75"/>
+      <c r="N6" s="75"/>
+      <c r="O6" s="71"/>
+      <c r="P6" s="74" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" s="74"/>
     </row>
     <row r="7" spans="2:17">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="103" t="s">
-        <v>81</v>
+      <c r="C7" s="58" t="s">
+        <v>84</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="109"/>
-      <c r="H7" s="112"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="73"/>
       <c r="I7" s="18" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M7" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="N7" s="76"/>
-      <c r="O7" s="78"/>
-      <c r="P7" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q7" s="78"/>
+        <v>93</v>
+      </c>
+      <c r="N7" s="70"/>
+      <c r="O7" s="71"/>
+      <c r="P7" s="70" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q7" s="71"/>
     </row>
     <row r="8" spans="2:17">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="103"/>
+      <c r="C8" s="58"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G8" s="18">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I8" s="2">
         <v>123</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K8" s="2">
         <v>1</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="N8" s="95"/>
-      <c r="O8" s="96"/>
-      <c r="P8" s="95" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q8" s="96"/>
+        <v>96</v>
+      </c>
+      <c r="N8" s="68"/>
+      <c r="O8" s="69"/>
+      <c r="P8" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q8" s="69"/>
     </row>
     <row r="9" spans="2:17">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="103" t="s">
-        <v>83</v>
+      <c r="C9" s="58" t="s">
+        <v>86</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E9" s="4"/>
       <c r="G9" s="18">
         <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I9" s="2">
         <v>123</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K9" s="2">
         <v>-1</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N9" s="39"/>
       <c r="O9" s="40"/>
       <c r="P9" s="39" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="40"/>
     </row>
@@ -2522,36 +2527,36 @@
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="103"/>
+      <c r="C10" s="58"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G10" s="23">
         <v>3</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I10" s="2">
         <v>123</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N10" s="39"/>
       <c r="O10" s="40"/>
       <c r="P10" s="39" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q10" s="40"/>
     </row>
@@ -2559,38 +2564,38 @@
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="100" t="s">
-        <v>85</v>
+      <c r="C11" s="55" t="s">
+        <v>88</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E11" s="4"/>
       <c r="G11" s="23">
         <v>4</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I11" s="2">
         <v>123</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N11" s="39"/>
       <c r="O11" s="40"/>
       <c r="P11" s="41" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q11" s="42"/>
     </row>
@@ -2598,36 +2603,36 @@
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="102"/>
+      <c r="C12" s="57"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G12" s="10">
         <v>5</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I12" s="2">
         <v>123</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K12" s="2">
         <v>1</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N12" s="39"/>
       <c r="O12" s="40"/>
       <c r="P12" s="41" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q12" s="42"/>
     </row>
@@ -2635,49 +2640,49 @@
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="100" t="s">
-        <v>110</v>
+      <c r="C13" s="55" t="s">
+        <v>113</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E13" s="4"/>
       <c r="G13" s="10">
         <v>6</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I13" s="2">
         <v>123</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K13" s="2">
         <v>1</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="N13" s="110"/>
-      <c r="O13" s="111"/>
-      <c r="P13" s="110" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q13" s="111"/>
+        <v>96</v>
+      </c>
+      <c r="N13" s="66"/>
+      <c r="O13" s="67"/>
+      <c r="P13" s="66" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q13" s="67"/>
     </row>
     <row r="14" spans="2:17">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="101"/>
+      <c r="C14" s="56"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G14" s="23">
         <v>7</v>
@@ -2687,10 +2692,10 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="102"/>
+      <c r="C15" s="57"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G15" s="14">
         <v>8</v>
@@ -2701,10 +2706,10 @@
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
-      <c r="N15" s="95"/>
-      <c r="O15" s="96"/>
-      <c r="P15" s="98"/>
-      <c r="Q15" s="99"/>
+      <c r="N15" s="68"/>
+      <c r="O15" s="69"/>
+      <c r="P15" s="77"/>
+      <c r="Q15" s="78"/>
     </row>
     <row r="16" spans="2:17">
       <c r="B16" s="4">
@@ -2720,17 +2725,17 @@
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
       <c r="M16" s="13"/>
-      <c r="N16" s="95"/>
-      <c r="O16" s="96"/>
-      <c r="P16" s="98"/>
-      <c r="Q16" s="99"/>
+      <c r="N16" s="68"/>
+      <c r="O16" s="69"/>
+      <c r="P16" s="77"/>
+      <c r="Q16" s="78"/>
     </row>
     <row r="17" spans="2:17">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="103" t="s">
-        <v>32</v>
+      <c r="C17" s="58" t="s">
+        <v>35</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -2741,16 +2746,16 @@
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
-      <c r="N17" s="95"/>
-      <c r="O17" s="96"/>
-      <c r="P17" s="98"/>
-      <c r="Q17" s="99"/>
+      <c r="N17" s="68"/>
+      <c r="O17" s="69"/>
+      <c r="P17" s="77"/>
+      <c r="Q17" s="78"/>
     </row>
     <row r="18" spans="2:17">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="103"/>
+      <c r="C18" s="58"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="G18" s="14"/>
@@ -2760,17 +2765,17 @@
       <c r="K18" s="13"/>
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
-      <c r="N18" s="95"/>
-      <c r="O18" s="96"/>
-      <c r="P18" s="98"/>
-      <c r="Q18" s="99"/>
+      <c r="N18" s="68"/>
+      <c r="O18" s="69"/>
+      <c r="P18" s="77"/>
+      <c r="Q18" s="78"/>
     </row>
     <row r="19" spans="2:17">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="103" t="s">
-        <v>32</v>
+      <c r="C19" s="58" t="s">
+        <v>35</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -2781,28 +2786,43 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="95"/>
-      <c r="O19" s="96"/>
-      <c r="P19" s="98"/>
-      <c r="Q19" s="99"/>
+      <c r="N19" s="68"/>
+      <c r="O19" s="69"/>
+      <c r="P19" s="77"/>
+      <c r="Q19" s="78"/>
     </row>
     <row r="20" spans="2:17">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="103"/>
+      <c r="C20" s="58"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
     <row r="22" spans="2:17">
       <c r="D22" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22" s="97"/>
-      <c r="G22" s="97"/>
+        <v>40</v>
+      </c>
+      <c r="F22" s="76"/>
+      <c r="G22" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P15:Q15"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="C19:C20"/>
@@ -2819,28 +2839,13 @@
     <mergeCell ref="P8:Q8"/>
     <mergeCell ref="N7:O7"/>
     <mergeCell ref="H6:H7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P15:Q15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
@@ -2866,121 +2871,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18">
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="53"/>
     </row>
     <row r="3" spans="2:18">
-      <c r="B3" s="104" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="106"/>
+      <c r="B3" s="59" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="61"/>
     </row>
     <row r="5" spans="2:18">
-      <c r="B5" s="119" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="119"/>
-      <c r="D5" s="119"/>
+      <c r="B5" s="84" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="108" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
-      <c r="L5" s="108"/>
-      <c r="M5" s="108"/>
-      <c r="N5" s="108"/>
-      <c r="O5" s="108"/>
-      <c r="P5" s="108"/>
-      <c r="Q5" s="108"/>
-      <c r="R5" s="108"/>
+      <c r="G5" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
+      <c r="P5" s="63"/>
+      <c r="Q5" s="63"/>
+      <c r="R5" s="63"/>
     </row>
     <row r="6" spans="2:18" ht="14.4" customHeight="1">
       <c r="B6" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E6" s="8"/>
-      <c r="G6" s="59" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="88" t="s">
+      <c r="G6" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="115" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="116"/>
-      <c r="M6" s="116"/>
-      <c r="N6" s="116"/>
-      <c r="O6" s="116"/>
-      <c r="P6" s="117"/>
-      <c r="Q6" s="115" t="s">
-        <v>28</v>
-      </c>
-      <c r="R6" s="117"/>
+      <c r="H6" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="64" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="72" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" s="85" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="93"/>
+      <c r="M6" s="93"/>
+      <c r="N6" s="93"/>
+      <c r="O6" s="93"/>
+      <c r="P6" s="86"/>
+      <c r="Q6" s="85" t="s">
+        <v>31</v>
+      </c>
+      <c r="R6" s="86"/>
     </row>
     <row r="7" spans="2:18">
-      <c r="B7" s="100">
+      <c r="B7" s="55">
         <v>1</v>
       </c>
-      <c r="C7" s="124" t="s">
-        <v>109</v>
+      <c r="C7" s="79" t="s">
+        <v>112</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G7" s="109"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="109"/>
-      <c r="J7" s="112"/>
+        <v>106</v>
+      </c>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="65"/>
+      <c r="J7" s="73"/>
       <c r="K7" s="18" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="M7" s="18" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="N7" s="18" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="P7" s="18"/>
-      <c r="Q7" s="76" t="s">
-        <v>45</v>
-      </c>
-      <c r="R7" s="78"/>
+      <c r="Q7" s="70" t="s">
+        <v>48</v>
+      </c>
+      <c r="R7" s="71"/>
     </row>
     <row r="8" spans="2:18">
-      <c r="B8" s="101"/>
-      <c r="C8" s="125"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="80"/>
       <c r="D8" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G8" s="18">
         <v>1</v>
@@ -2989,7 +2994,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J8" s="11"/>
       <c r="K8" s="22"/>
@@ -2998,14 +3003,14 @@
       <c r="N8" s="22"/>
       <c r="O8" s="22"/>
       <c r="P8" s="22"/>
-      <c r="Q8" s="113"/>
-      <c r="R8" s="114"/>
+      <c r="Q8" s="87"/>
+      <c r="R8" s="88"/>
     </row>
     <row r="9" spans="2:18">
-      <c r="B9" s="101"/>
-      <c r="C9" s="125"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="80"/>
       <c r="D9" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G9" s="14">
         <v>2</v>
@@ -3015,34 +3020,34 @@
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K9" s="2">
         <v>123</v>
       </c>
       <c r="L9" s="17" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M9" s="22">
         <v>7</v>
       </c>
       <c r="N9" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="P9" s="13"/>
-      <c r="Q9" s="122" t="s">
-        <v>35</v>
-      </c>
-      <c r="R9" s="123"/>
+      <c r="Q9" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="R9" s="92"/>
     </row>
     <row r="10" spans="2:18">
-      <c r="B10" s="101"/>
-      <c r="C10" s="125"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="80"/>
       <c r="D10" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G10" s="18">
         <v>3</v>
@@ -3056,28 +3061,28 @@
         <v>123</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M10" s="22">
         <v>7</v>
       </c>
       <c r="N10" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="P10" s="22"/>
-      <c r="Q10" s="113" t="s">
-        <v>31</v>
-      </c>
-      <c r="R10" s="114"/>
+      <c r="Q10" s="87" t="s">
+        <v>34</v>
+      </c>
+      <c r="R10" s="88"/>
     </row>
     <row r="11" spans="2:18">
-      <c r="B11" s="101"/>
-      <c r="C11" s="125"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="80"/>
       <c r="D11" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G11" s="18">
         <v>4</v>
@@ -3091,28 +3096,28 @@
         <v>123</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M11" s="22">
         <v>7</v>
       </c>
       <c r="N11" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="P11" s="22"/>
-      <c r="Q11" s="113" t="s">
-        <v>31</v>
-      </c>
-      <c r="R11" s="114"/>
+      <c r="Q11" s="87" t="s">
+        <v>34</v>
+      </c>
+      <c r="R11" s="88"/>
     </row>
     <row r="12" spans="2:18">
-      <c r="B12" s="102"/>
-      <c r="C12" s="126"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="81"/>
       <c r="D12" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G12" s="18">
         <v>5</v>
@@ -3126,32 +3131,32 @@
         <v>123</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M12" s="22">
         <v>7</v>
       </c>
       <c r="N12" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="P12" s="22"/>
-      <c r="Q12" s="113" t="s">
-        <v>31</v>
-      </c>
-      <c r="R12" s="114"/>
+      <c r="Q12" s="87" t="s">
+        <v>34</v>
+      </c>
+      <c r="R12" s="88"/>
     </row>
     <row r="13" spans="2:18">
-      <c r="B13" s="100">
+      <c r="B13" s="55">
         <v>2</v>
       </c>
-      <c r="C13" s="124" t="s">
-        <v>85</v>
+      <c r="C13" s="79" t="s">
+        <v>88</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G13" s="14">
         <v>6</v>
@@ -3165,28 +3170,28 @@
         <v>123</v>
       </c>
       <c r="L13" s="45" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M13" s="22">
         <v>7</v>
       </c>
       <c r="N13" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="P13" s="13"/>
-      <c r="Q13" s="110" t="s">
-        <v>114</v>
-      </c>
-      <c r="R13" s="111"/>
+      <c r="Q13" s="66" t="s">
+        <v>117</v>
+      </c>
+      <c r="R13" s="67"/>
     </row>
     <row r="14" spans="2:18">
-      <c r="B14" s="101"/>
-      <c r="C14" s="125"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="80"/>
       <c r="D14" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G14" s="18">
         <v>7</v>
@@ -3195,7 +3200,7 @@
         <v>7</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J14" s="11"/>
       <c r="K14" s="22"/>
@@ -3204,14 +3209,14 @@
       <c r="N14" s="22"/>
       <c r="O14" s="22"/>
       <c r="P14" s="22"/>
-      <c r="Q14" s="113"/>
-      <c r="R14" s="114"/>
+      <c r="Q14" s="87"/>
+      <c r="R14" s="88"/>
     </row>
     <row r="15" spans="2:18">
-      <c r="B15" s="101"/>
-      <c r="C15" s="125"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="80"/>
       <c r="D15" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G15" s="18">
         <v>8</v>
@@ -3225,7 +3230,7 @@
         <v>123</v>
       </c>
       <c r="L15" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="M15" s="22">
         <v>0</v>
@@ -3233,16 +3238,16 @@
       <c r="N15" s="22"/>
       <c r="O15" s="22"/>
       <c r="P15" s="22"/>
-      <c r="Q15" s="120" t="s">
-        <v>97</v>
-      </c>
-      <c r="R15" s="121"/>
+      <c r="Q15" s="89" t="s">
+        <v>100</v>
+      </c>
+      <c r="R15" s="90"/>
     </row>
     <row r="16" spans="2:18">
-      <c r="B16" s="101"/>
-      <c r="C16" s="125"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="80"/>
       <c r="D16" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G16" s="18">
         <v>9</v>
@@ -3251,7 +3256,7 @@
         <v>9</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J16" s="11"/>
       <c r="K16" s="22"/>
@@ -3260,16 +3265,16 @@
       <c r="N16" s="22"/>
       <c r="O16" s="22"/>
       <c r="P16" s="22"/>
-      <c r="Q16" s="113" t="s">
-        <v>31</v>
-      </c>
-      <c r="R16" s="114"/>
+      <c r="Q16" s="87" t="s">
+        <v>34</v>
+      </c>
+      <c r="R16" s="88"/>
     </row>
     <row r="17" spans="2:18">
-      <c r="B17" s="101"/>
-      <c r="C17" s="125"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="80"/>
       <c r="D17" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G17" s="18">
         <v>10</v>
@@ -3282,28 +3287,28 @@
         <v>123</v>
       </c>
       <c r="L17" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="N17" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="P17" s="22"/>
-      <c r="Q17" s="113" t="s">
-        <v>31</v>
-      </c>
-      <c r="R17" s="114"/>
+      <c r="Q17" s="87" t="s">
+        <v>34</v>
+      </c>
+      <c r="R17" s="88"/>
     </row>
     <row r="18" spans="2:18">
-      <c r="B18" s="102"/>
-      <c r="C18" s="126"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="81"/>
       <c r="D18" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G18" s="18">
         <v>11</v>
@@ -3313,34 +3318,34 @@
       </c>
       <c r="I18" s="11"/>
       <c r="J18" s="16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K18" s="22">
         <v>123</v>
       </c>
       <c r="L18" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="M18" s="22" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N18" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="P18" s="22"/>
-      <c r="Q18" s="122" t="s">
-        <v>35</v>
-      </c>
-      <c r="R18" s="123"/>
+      <c r="Q18" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="R18" s="92"/>
     </row>
     <row r="19" spans="2:18">
-      <c r="B19" s="100">
+      <c r="B19" s="55">
         <v>3</v>
       </c>
-      <c r="C19" s="124"/>
+      <c r="C19" s="79"/>
       <c r="D19" s="2"/>
       <c r="G19" s="18">
         <v>12</v>
@@ -3354,26 +3359,26 @@
         <v>123</v>
       </c>
       <c r="L19" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="M19" s="22" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N19" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="P19" s="22"/>
-      <c r="Q19" s="113" t="s">
-        <v>31</v>
-      </c>
-      <c r="R19" s="114"/>
+      <c r="Q19" s="87" t="s">
+        <v>34</v>
+      </c>
+      <c r="R19" s="88"/>
     </row>
     <row r="20" spans="2:18">
-      <c r="B20" s="101"/>
-      <c r="C20" s="125"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="80"/>
       <c r="D20" s="2"/>
       <c r="G20" s="18">
         <v>13</v>
@@ -3387,12 +3392,12 @@
       <c r="N20" s="22"/>
       <c r="O20" s="22"/>
       <c r="P20" s="22"/>
-      <c r="Q20" s="113"/>
-      <c r="R20" s="114"/>
+      <c r="Q20" s="87"/>
+      <c r="R20" s="88"/>
     </row>
     <row r="21" spans="2:18">
-      <c r="B21" s="101"/>
-      <c r="C21" s="125"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="80"/>
       <c r="D21" s="2"/>
       <c r="G21" s="18">
         <v>14</v>
@@ -3406,12 +3411,12 @@
       <c r="N21" s="22"/>
       <c r="O21" s="22"/>
       <c r="P21" s="22"/>
-      <c r="Q21" s="113"/>
-      <c r="R21" s="114"/>
+      <c r="Q21" s="87"/>
+      <c r="R21" s="88"/>
     </row>
     <row r="22" spans="2:18">
-      <c r="B22" s="101"/>
-      <c r="C22" s="125"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="80"/>
       <c r="D22" s="2"/>
       <c r="G22" s="18">
         <v>15</v>
@@ -3425,12 +3430,12 @@
       <c r="N22" s="22"/>
       <c r="O22" s="22"/>
       <c r="P22" s="22"/>
-      <c r="Q22" s="113"/>
-      <c r="R22" s="114"/>
+      <c r="Q22" s="87"/>
+      <c r="R22" s="88"/>
     </row>
     <row r="23" spans="2:18">
-      <c r="B23" s="101"/>
-      <c r="C23" s="125"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="80"/>
       <c r="D23" s="2"/>
       <c r="G23" s="18">
         <v>16</v>
@@ -3444,12 +3449,12 @@
       <c r="N23" s="22"/>
       <c r="O23" s="22"/>
       <c r="P23" s="22"/>
-      <c r="Q23" s="113"/>
-      <c r="R23" s="114"/>
+      <c r="Q23" s="87"/>
+      <c r="R23" s="88"/>
     </row>
     <row r="24" spans="2:18">
-      <c r="B24" s="102"/>
-      <c r="C24" s="126"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="81"/>
       <c r="D24" s="2"/>
       <c r="G24" s="18">
         <v>17</v>
@@ -3463,25 +3468,25 @@
       <c r="N24" s="22"/>
       <c r="O24" s="22"/>
       <c r="P24" s="22"/>
-      <c r="Q24" s="113"/>
-      <c r="R24" s="114"/>
+      <c r="Q24" s="87"/>
+      <c r="R24" s="88"/>
     </row>
     <row r="25" spans="2:18">
-      <c r="B25" s="100">
+      <c r="B25" s="55">
         <v>4</v>
       </c>
-      <c r="C25" s="124" t="s">
-        <v>32</v>
+      <c r="C25" s="79" t="s">
+        <v>35</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G25" s="18">
         <v>18</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="11" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="22"/>
@@ -3490,60 +3495,84 @@
       <c r="N25" s="22"/>
       <c r="O25" s="22"/>
       <c r="P25" s="22"/>
-      <c r="Q25" s="113"/>
-      <c r="R25" s="114"/>
+      <c r="Q25" s="87"/>
+      <c r="R25" s="88"/>
     </row>
     <row r="26" spans="2:18">
-      <c r="B26" s="101"/>
-      <c r="C26" s="125"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="80"/>
       <c r="D26" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="2:18">
-      <c r="B27" s="101"/>
-      <c r="C27" s="125"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="80"/>
       <c r="D27" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="2:18">
-      <c r="B28" s="101"/>
-      <c r="C28" s="125"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="80"/>
       <c r="D28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G28" s="97"/>
-      <c r="H28" s="97"/>
-      <c r="I28" s="118"/>
-      <c r="J28" s="118"/>
-      <c r="K28" s="118"/>
-      <c r="L28" s="118"/>
-      <c r="M28" s="118"/>
+        <v>35</v>
+      </c>
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="83"/>
+      <c r="K28" s="83"/>
+      <c r="L28" s="83"/>
+      <c r="M28" s="83"/>
       <c r="N28" s="30"/>
     </row>
     <row r="29" spans="2:18">
-      <c r="B29" s="101"/>
-      <c r="C29" s="125"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="80"/>
       <c r="D29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="127"/>
-      <c r="J29" s="127"/>
-      <c r="K29" s="127"/>
-      <c r="L29" s="127"/>
-      <c r="M29" s="127"/>
+        <v>35</v>
+      </c>
+      <c r="I29" s="82"/>
+      <c r="J29" s="82"/>
+      <c r="K29" s="82"/>
+      <c r="L29" s="82"/>
+      <c r="M29" s="82"/>
       <c r="N29" s="31"/>
     </row>
     <row r="30" spans="2:18">
-      <c r="B30" s="102"/>
-      <c r="C30" s="126"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="81"/>
       <c r="D30" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:M28"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="Q9:R9"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="I6:I7"/>
@@ -3560,30 +3589,6 @@
     <mergeCell ref="G5:R5"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I28:M28"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q12:R12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3592,7 +3597,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
@@ -3610,121 +3615,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14">
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="53"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="92" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
-      <c r="I3" s="92"/>
-      <c r="J3" s="92"/>
-      <c r="K3" s="92"/>
-      <c r="L3" s="92"/>
-      <c r="M3" s="92"/>
-      <c r="N3" s="92"/>
+      <c r="B3" s="107" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="107"/>
+      <c r="N3" s="107"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="59" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="90" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="61" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="88" t="s">
+      <c r="B4" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="78"/>
-      <c r="M4" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="N4" s="72"/>
+      <c r="C4" s="105" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="103" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="72" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="74" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" s="74"/>
     </row>
     <row r="5" spans="2:14">
-      <c r="B5" s="60"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="89"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="104"/>
       <c r="F5" s="43" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G5" s="43" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H5" s="43" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I5" s="43" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J5" s="43" t="s">
-        <v>90</v>
-      </c>
-      <c r="K5" s="73"/>
-      <c r="L5" s="61"/>
+        <v>93</v>
+      </c>
+      <c r="K5" s="102"/>
+      <c r="L5" s="103"/>
       <c r="M5" s="43" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="N5" s="43" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="2:14">
       <c r="B6" s="9">
         <v>1</v>
       </c>
-      <c r="C6" s="82" t="s">
-        <v>58</v>
+      <c r="C6" s="99" t="s">
+        <v>61</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F6" s="2">
         <v>123</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
       </c>
-      <c r="I6" s="46" t="s">
-        <v>92</v>
+      <c r="I6" s="48" t="s">
+        <v>95</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
+        <v>96</v>
+      </c>
+      <c r="K6" s="94"/>
+      <c r="L6" s="94"/>
       <c r="M6" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="2:14">
@@ -3732,35 +3737,35 @@
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="83"/>
+      <c r="C7" s="100"/>
       <c r="D7" s="18" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F7" s="2">
         <v>123</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2">
         <v>-1</v>
       </c>
       <c r="I7" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K7" s="79"/>
-      <c r="L7" s="79"/>
-      <c r="M7" s="49" t="s">
-        <v>141</v>
+        <v>96</v>
+      </c>
+      <c r="K7" s="95"/>
+      <c r="L7" s="95"/>
+      <c r="M7" s="129" t="s">
+        <v>144</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="2:14">
@@ -3768,35 +3773,35 @@
         <f t="shared" ref="B8:B20" si="0">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="83"/>
+      <c r="C8" s="100"/>
       <c r="D8" s="18" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F8" s="2">
         <v>123</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
       </c>
       <c r="I8" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
-      <c r="M8" s="49" t="s">
-        <v>145</v>
+      <c r="M8" s="129" t="s">
+        <v>148</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="2:14">
@@ -3804,35 +3809,35 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="83"/>
+      <c r="C9" s="100"/>
       <c r="D9" s="18" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F9" s="2">
         <v>123</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I9" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K9" s="80"/>
-      <c r="L9" s="80"/>
+        <v>96</v>
+      </c>
+      <c r="K9" s="96"/>
+      <c r="L9" s="96"/>
       <c r="M9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N9" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="10" spans="2:14">
@@ -3840,35 +3845,35 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C10" s="83"/>
+      <c r="C10" s="100"/>
       <c r="D10" s="18" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F10" s="2">
         <v>123</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K10" s="75"/>
-      <c r="L10" s="75"/>
-      <c r="M10" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="K10" s="97"/>
+      <c r="L10" s="97"/>
+      <c r="M10" s="129" t="s">
+        <v>38</v>
+      </c>
+      <c r="N10" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="11" spans="2:14">
@@ -3876,35 +3881,35 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C11" s="83"/>
+      <c r="C11" s="100"/>
       <c r="D11" s="18" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F11" s="2">
         <v>123</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K11" s="75"/>
-      <c r="L11" s="75"/>
+        <v>96</v>
+      </c>
+      <c r="K11" s="97"/>
+      <c r="L11" s="97"/>
       <c r="M11" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="2:14">
@@ -3912,35 +3917,35 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C12" s="83"/>
+      <c r="C12" s="100"/>
       <c r="D12" s="18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F12" s="2">
         <v>123</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H12" s="22">
         <v>7</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K12" s="75"/>
-      <c r="L12" s="75"/>
+        <v>96</v>
+      </c>
+      <c r="K12" s="97"/>
+      <c r="L12" s="97"/>
       <c r="M12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="N12" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="13" spans="2:14">
@@ -3948,35 +3953,35 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C13" s="83"/>
+      <c r="C13" s="100"/>
       <c r="D13" s="18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F13" s="2">
         <v>123</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H13" s="22">
         <v>7</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K13" s="80"/>
-      <c r="L13" s="80"/>
-      <c r="M13" s="48" t="s">
-        <v>31</v>
+        <v>96</v>
+      </c>
+      <c r="K13" s="96"/>
+      <c r="L13" s="96"/>
+      <c r="M13" s="128" t="s">
+        <v>34</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="2:14">
@@ -3984,35 +3989,35 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C14" s="83"/>
+      <c r="C14" s="100"/>
       <c r="D14" s="18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F14" s="2">
         <v>123</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H14" s="22">
         <v>7</v>
       </c>
-      <c r="I14" s="46" t="s">
-        <v>92</v>
+      <c r="I14" s="48" t="s">
+        <v>95</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K14" s="74"/>
-      <c r="L14" s="74"/>
+        <v>96</v>
+      </c>
+      <c r="K14" s="94"/>
+      <c r="L14" s="94"/>
       <c r="M14" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="14.4" customHeight="1">
@@ -4020,35 +4025,35 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C15" s="83"/>
+      <c r="C15" s="100"/>
       <c r="D15" s="18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F15" s="2">
         <v>123</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H15" s="22">
         <v>7</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K15" s="79"/>
-      <c r="L15" s="79"/>
-      <c r="M15" s="49" t="s">
-        <v>31</v>
+        <v>96</v>
+      </c>
+      <c r="K15" s="95"/>
+      <c r="L15" s="95"/>
+      <c r="M15" s="129" t="s">
+        <v>34</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="2:14">
@@ -4056,35 +4061,35 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C16" s="83"/>
+      <c r="C16" s="100"/>
       <c r="D16" s="18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F16" s="2">
         <v>123</v>
       </c>
       <c r="G16" s="45" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H16" s="22">
         <v>7</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
-      <c r="M16" s="49" t="s">
-        <v>142</v>
+      <c r="M16" s="129" t="s">
+        <v>145</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="2:16">
@@ -4092,35 +4097,35 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C17" s="83"/>
+      <c r="C17" s="100"/>
       <c r="D17" s="18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F17" s="2">
         <v>123</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H17" s="22">
         <v>0</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K17" s="80"/>
-      <c r="L17" s="80"/>
-      <c r="M17" s="48" t="s">
-        <v>144</v>
+        <v>96</v>
+      </c>
+      <c r="K17" s="96"/>
+      <c r="L17" s="96"/>
+      <c r="M17" s="128" t="s">
+        <v>147</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="14.4" customHeight="1">
@@ -4128,35 +4133,35 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C18" s="83"/>
+      <c r="C18" s="100"/>
       <c r="D18" s="18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F18" s="2">
         <v>123</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I18" s="46" t="s">
-        <v>92</v>
+        <v>130</v>
+      </c>
+      <c r="I18" s="48" t="s">
+        <v>95</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K18" s="75"/>
-      <c r="L18" s="75"/>
-      <c r="M18" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="K18" s="97"/>
+      <c r="L18" s="97"/>
+      <c r="M18" s="129" t="s">
+        <v>38</v>
+      </c>
+      <c r="N18" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="N18" s="9" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="19" spans="2:16">
@@ -4164,35 +4169,35 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C19" s="83"/>
+      <c r="C19" s="100"/>
       <c r="D19" s="18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F19" s="2">
         <v>123</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I19" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K19" s="75"/>
-      <c r="L19" s="75"/>
+        <v>96</v>
+      </c>
+      <c r="K19" s="97"/>
+      <c r="L19" s="97"/>
       <c r="M19" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="2:16">
@@ -4200,55 +4205,55 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C20" s="84"/>
+      <c r="C20" s="101"/>
       <c r="D20" s="18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F20" s="2">
         <v>123</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I20" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K20" s="75"/>
-      <c r="L20" s="75"/>
+        <v>96</v>
+      </c>
+      <c r="K20" s="97"/>
+      <c r="L20" s="97"/>
       <c r="M20" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="2:16">
-      <c r="B21" s="19"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="81"/>
-      <c r="L21" s="81"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="98"/>
+      <c r="L21" s="98"/>
+      <c r="M21" s="46"/>
+      <c r="N21" s="46"/>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" s="19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="20"/>
@@ -4258,102 +4263,102 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="58"/>
+      <c r="K23" s="108"/>
+      <c r="L23" s="108"/>
       <c r="M23" s="7"/>
     </row>
     <row r="24" spans="2:16" ht="15" thickBot="1">
       <c r="M24" s="7"/>
     </row>
     <row r="25" spans="2:16" ht="15" thickTop="1">
-      <c r="C25" s="52" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="55"/>
+      <c r="C25" s="117" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="118"/>
+      <c r="E25" s="118"/>
+      <c r="F25" s="119"/>
       <c r="G25" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="H25" s="52" t="s">
-        <v>68</v>
-      </c>
-      <c r="I25" s="53"/>
-      <c r="J25" s="54"/>
-      <c r="K25" s="54"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="N25" s="53"/>
-      <c r="O25" s="54"/>
-      <c r="P25" s="55"/>
+        <v>70</v>
+      </c>
+      <c r="H25" s="117" t="s">
+        <v>71</v>
+      </c>
+      <c r="I25" s="120"/>
+      <c r="J25" s="118"/>
+      <c r="K25" s="118"/>
+      <c r="L25" s="119"/>
+      <c r="M25" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="N25" s="120"/>
+      <c r="O25" s="118"/>
+      <c r="P25" s="119"/>
     </row>
     <row r="26" spans="2:16">
-      <c r="B26" s="65" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="66" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="50" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="F26" s="51" t="s">
+      <c r="B26" s="113" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="114" t="s">
         <v>73</v>
       </c>
-      <c r="G26" s="71" t="s">
+      <c r="D26" s="115" t="s">
         <v>74</v>
       </c>
-      <c r="H26" s="67" t="s">
+      <c r="E26" s="115" t="s">
         <v>75</v>
       </c>
-      <c r="I26" s="68"/>
-      <c r="J26" s="50" t="s">
-        <v>70</v>
-      </c>
-      <c r="K26" s="50" t="s">
-        <v>71</v>
-      </c>
-      <c r="L26" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="M26" s="56" t="s">
+      <c r="F26" s="116" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="125" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26" s="121" t="s">
+        <v>78</v>
+      </c>
+      <c r="I26" s="122"/>
+      <c r="J26" s="115" t="s">
+        <v>73</v>
+      </c>
+      <c r="K26" s="115" t="s">
+        <v>74</v>
+      </c>
+      <c r="L26" s="116" t="s">
         <v>75</v>
       </c>
-      <c r="N26" s="50" t="s">
-        <v>70</v>
-      </c>
-      <c r="O26" s="50" t="s">
-        <v>71</v>
-      </c>
-      <c r="P26" s="51" t="s">
-        <v>72</v>
+      <c r="M26" s="126" t="s">
+        <v>78</v>
+      </c>
+      <c r="N26" s="115" t="s">
+        <v>73</v>
+      </c>
+      <c r="O26" s="115" t="s">
+        <v>74</v>
+      </c>
+      <c r="P26" s="116" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="2:16">
-      <c r="B27" s="65"/>
-      <c r="C27" s="66"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="69"/>
-      <c r="I27" s="70"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="51"/>
-      <c r="M27" s="57"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="50"/>
-      <c r="P27" s="51"/>
+      <c r="B27" s="113"/>
+      <c r="C27" s="114"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="116"/>
+      <c r="G27" s="125"/>
+      <c r="H27" s="123"/>
+      <c r="I27" s="124"/>
+      <c r="J27" s="115"/>
+      <c r="K27" s="115"/>
+      <c r="L27" s="116"/>
+      <c r="M27" s="127"/>
+      <c r="N27" s="115"/>
+      <c r="O27" s="115"/>
+      <c r="P27" s="116"/>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" s="29" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C28" s="25">
         <v>15</v>
@@ -4362,15 +4367,15 @@
       <c r="E28" s="27"/>
       <c r="F28" s="28"/>
       <c r="G28" s="33"/>
-      <c r="H28" s="63" t="s">
-        <v>76</v>
-      </c>
-      <c r="I28" s="64"/>
+      <c r="H28" s="111" t="s">
+        <v>79</v>
+      </c>
+      <c r="I28" s="112"/>
       <c r="J28" s="2"/>
       <c r="K28" s="27"/>
       <c r="L28" s="28"/>
       <c r="M28" s="32" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="27"/>
@@ -4378,28 +4383,11 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="C6:C20"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="N26:N27"/>
     <mergeCell ref="K23:L23"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="D4:D5"/>
@@ -4416,11 +4404,28 @@
     <mergeCell ref="G26:G27"/>
     <mergeCell ref="K26:K27"/>
     <mergeCell ref="L26:L27"/>
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="M25:P25"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="N26:N27"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="C6:C20"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K19:L19"/>
   </mergeCells>
   <phoneticPr fontId="29" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4430,21 +4435,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="798a38e6de461387c626d04793181ea9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="301f98df-4edd-4096-94f8-2f8af3eee570" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b4b8dab68acb31e3ac71f6347d499c29" ns2:_="">
     <xsd:import namespace="301f98df-4edd-4096-94f8-2f8af3eee570"/>
@@ -4582,10 +4572,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E854E7-906F-4C7C-AFC0-1BC802AE88F0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4607,19 +4622,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E854E7-906F-4C7C-AFC0-1BC802AE88F0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>